--- a/research/traditional_assets/database/data/hungary/hungary_computer_services.xlsx
+++ b/research/traditional_assets/database/data/hungary/hungary_computer_services.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.11399278759394</v>
+        <v>0.1139311440851054</v>
       </c>
       <c r="C2">
-        <v>3509.952006348534</v>
+        <v>3478.815587840837</v>
       </c>
       <c r="D2">
-        <v>3203.152006348534</v>
+        <v>3204.757587840837</v>
       </c>
       <c r="E2">
-        <v>-2589.3</v>
+        <v>-2556.558</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32.742</v>
       </c>
       <c r="G2">
         <v>306.8</v>
@@ -1439,28 +1439,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.6469226</v>
       </c>
       <c r="N2">
-        <v>522.9000000000001</v>
+        <v>521.2530774000001</v>
       </c>
       <c r="O2">
-        <v>47.06100000000001</v>
+        <v>46.912776966</v>
       </c>
       <c r="P2">
-        <v>475.8390000000001</v>
+        <v>474.340300434</v>
       </c>
       <c r="Q2">
-        <v>1019.139</v>
+        <v>1017.640300434</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.11399278759394</v>
+        <v>0.1146196101869752</v>
       </c>
       <c r="T2">
-        <v>0.9922881498763957</v>
+        <v>1.001409182365159</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>317.5012596220369</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1139311440851054</v>
+        <v>0.1138695005762709</v>
       </c>
       <c r="C3">
-        <v>3478.815587840837</v>
+        <v>3447.680779737356</v>
       </c>
       <c r="D3">
-        <v>3204.757587840837</v>
+        <v>3206.364779737356</v>
       </c>
       <c r="E3">
-        <v>-2556.558</v>
+        <v>-2523.816</v>
       </c>
       <c r="F3">
-        <v>32.742</v>
+        <v>65.48400000000001</v>
       </c>
       <c r="G3">
         <v>306.8</v>
@@ -1521,28 +1521,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M3">
-        <v>1.6469226</v>
+        <v>3.2938452</v>
       </c>
       <c r="N3">
-        <v>521.2530774000001</v>
+        <v>519.6061548000001</v>
       </c>
       <c r="O3">
-        <v>46.912776966</v>
+        <v>46.76455393200001</v>
       </c>
       <c r="P3">
-        <v>474.340300434</v>
+        <v>472.8416008680001</v>
       </c>
       <c r="Q3">
-        <v>1017.640300434</v>
+        <v>1016.141600868</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1146196101869752</v>
+        <v>0.1152592250778275</v>
       </c>
       <c r="T3">
-        <v>1.001409182365159</v>
+        <v>1.0107163583741</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>317.5012596220369</v>
+        <v>158.7506298110185</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1138695005762709</v>
+        <v>0.1138078570674363</v>
       </c>
       <c r="C4">
-        <v>3447.680779737356</v>
+        <v>3416.547584462167</v>
       </c>
       <c r="D4">
-        <v>3206.364779737356</v>
+        <v>3207.973584462167</v>
       </c>
       <c r="E4">
-        <v>-2523.816</v>
+        <v>-2491.074</v>
       </c>
       <c r="F4">
-        <v>65.48400000000001</v>
+        <v>98.226</v>
       </c>
       <c r="G4">
         <v>306.8</v>
@@ -1603,28 +1603,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M4">
-        <v>3.2938452</v>
+        <v>4.9407678</v>
       </c>
       <c r="N4">
-        <v>519.6061548000001</v>
+        <v>517.9592322000001</v>
       </c>
       <c r="O4">
-        <v>46.76455393200001</v>
+        <v>46.61633089800001</v>
       </c>
       <c r="P4">
-        <v>472.8416008680001</v>
+        <v>471.3429013020001</v>
       </c>
       <c r="Q4">
-        <v>1016.141600868</v>
+        <v>1014.642901302</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1152592250778275</v>
+        <v>0.1159120279045736</v>
       </c>
       <c r="T4">
-        <v>1.0107163583741</v>
+        <v>1.020215434919309</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>158.7506298110185</v>
+        <v>105.8337532073457</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1138078570674363</v>
+        <v>0.1137462135586018</v>
       </c>
       <c r="C5">
-        <v>3416.547584462167</v>
+        <v>3385.416004444218</v>
       </c>
       <c r="D5">
-        <v>3207.973584462167</v>
+        <v>3209.584004444217</v>
       </c>
       <c r="E5">
-        <v>-2491.074</v>
+        <v>-2458.332</v>
       </c>
       <c r="F5">
-        <v>98.226</v>
+        <v>130.968</v>
       </c>
       <c r="G5">
         <v>306.8</v>
@@ -1685,28 +1685,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M5">
-        <v>4.9407678</v>
+        <v>6.587690400000001</v>
       </c>
       <c r="N5">
-        <v>517.9592322000001</v>
+        <v>516.3123096</v>
       </c>
       <c r="O5">
-        <v>46.61633089800001</v>
+        <v>46.468107864</v>
       </c>
       <c r="P5">
-        <v>471.3429013020001</v>
+        <v>469.8442017360001</v>
       </c>
       <c r="Q5">
-        <v>1014.642901302</v>
+        <v>1013.144201736</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1159120279045736</v>
+        <v>0.1165784307902102</v>
       </c>
       <c r="T5">
-        <v>1.020215434919309</v>
+        <v>1.029912408892542</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>105.8337532073457</v>
+        <v>79.37531490550923</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1137462135586018</v>
+        <v>0.1136845700497673</v>
       </c>
       <c r="C6">
-        <v>3385.416004444218</v>
+        <v>3354.28604211733</v>
       </c>
       <c r="D6">
-        <v>3209.584004444217</v>
+        <v>3211.196042117329</v>
       </c>
       <c r="E6">
-        <v>-2458.332</v>
+        <v>-2425.59</v>
       </c>
       <c r="F6">
-        <v>130.968</v>
+        <v>163.71</v>
       </c>
       <c r="G6">
         <v>306.8</v>
@@ -1767,28 +1767,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M6">
-        <v>6.587690400000001</v>
+        <v>8.234613000000001</v>
       </c>
       <c r="N6">
-        <v>516.3123096</v>
+        <v>514.6653870000001</v>
       </c>
       <c r="O6">
-        <v>46.468107864</v>
+        <v>46.31988483000001</v>
       </c>
       <c r="P6">
-        <v>469.8442017360001</v>
+        <v>468.3455021700001</v>
       </c>
       <c r="Q6">
-        <v>1013.144201736</v>
+        <v>1011.64550217</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1165784307902102</v>
+        <v>0.1172588632102813</v>
       </c>
       <c r="T6">
-        <v>1.029912408892542</v>
+        <v>1.039813529686265</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>79.37531490550923</v>
+        <v>63.50025192440738</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1136845700497673</v>
+        <v>0.1136229265409327</v>
       </c>
       <c r="C7">
-        <v>3354.28604211733</v>
+        <v>3323.157699920223</v>
       </c>
       <c r="D7">
-        <v>3211.196042117329</v>
+        <v>3212.809699920223</v>
       </c>
       <c r="E7">
-        <v>-2425.59</v>
+        <v>-2392.848</v>
       </c>
       <c r="F7">
-        <v>163.71</v>
+        <v>196.452</v>
       </c>
       <c r="G7">
         <v>306.8</v>
@@ -1849,28 +1849,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M7">
-        <v>8.234613000000001</v>
+        <v>9.881535600000001</v>
       </c>
       <c r="N7">
-        <v>514.6653870000001</v>
+        <v>513.0184644000001</v>
       </c>
       <c r="O7">
-        <v>46.31988483000001</v>
+        <v>46.17166179600001</v>
       </c>
       <c r="P7">
-        <v>468.3455021700001</v>
+        <v>466.8468026040001</v>
       </c>
       <c r="Q7">
-        <v>1011.64550217</v>
+        <v>1010.146802604</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1172588632102813</v>
+        <v>0.1179537729158859</v>
       </c>
       <c r="T7">
-        <v>1.039813529686265</v>
+        <v>1.049925312624535</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>63.50025192440738</v>
+        <v>52.91687660367282</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1136229265409327</v>
+        <v>0.1135612830320982</v>
       </c>
       <c r="C8">
-        <v>3323.157699920223</v>
+        <v>3292.03098029652</v>
       </c>
       <c r="D8">
-        <v>3212.809699920223</v>
+        <v>3214.42498029652</v>
       </c>
       <c r="E8">
-        <v>-2392.848</v>
+        <v>-2360.106</v>
       </c>
       <c r="F8">
-        <v>196.452</v>
+        <v>229.194</v>
       </c>
       <c r="G8">
         <v>306.8</v>
@@ -1931,28 +1931,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M8">
-        <v>9.881535599999999</v>
+        <v>11.5284582</v>
       </c>
       <c r="N8">
-        <v>513.0184644000001</v>
+        <v>511.3715418000001</v>
       </c>
       <c r="O8">
-        <v>46.17166179600001</v>
+        <v>46.023438762</v>
       </c>
       <c r="P8">
-        <v>466.8468026040001</v>
+        <v>465.3481030380001</v>
       </c>
       <c r="Q8">
-        <v>1010.146802604</v>
+        <v>1008.648103038</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1179537729158859</v>
+        <v>0.1186636269162346</v>
       </c>
       <c r="T8">
-        <v>1.049925312624535</v>
+        <v>1.060254553260402</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>52.91687660367283</v>
+        <v>45.35732280314814</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1135612830320982</v>
+        <v>0.1134996395232636</v>
       </c>
       <c r="C9">
-        <v>3292.03098029652</v>
+        <v>3260.905885694757</v>
       </c>
       <c r="D9">
-        <v>3214.42498029652</v>
+        <v>3216.041885694757</v>
       </c>
       <c r="E9">
-        <v>-2360.106</v>
+        <v>-2327.364</v>
       </c>
       <c r="F9">
-        <v>229.194</v>
+        <v>261.936</v>
       </c>
       <c r="G9">
         <v>306.8</v>
@@ -2013,28 +2013,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M9">
-        <v>11.5284582</v>
+        <v>13.1753808</v>
       </c>
       <c r="N9">
-        <v>511.3715418000001</v>
+        <v>509.7246192000001</v>
       </c>
       <c r="O9">
-        <v>46.023438762</v>
+        <v>45.875215728</v>
       </c>
       <c r="P9">
-        <v>465.3481030380001</v>
+        <v>463.8494034720001</v>
       </c>
       <c r="Q9">
-        <v>1008.648103038</v>
+        <v>1007.149403472</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1186636269162346</v>
+        <v>0.1193889125252866</v>
       </c>
       <c r="T9">
-        <v>1.060254553260403</v>
+        <v>1.070808342605745</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>45.35732280314813</v>
+        <v>39.68765745275461</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1134996395232636</v>
+        <v>0.1134379960144291</v>
       </c>
       <c r="C10">
-        <v>3260.905885694757</v>
+        <v>3229.782418568403</v>
       </c>
       <c r="D10">
-        <v>3216.041885694757</v>
+        <v>3217.660418568402</v>
       </c>
       <c r="E10">
-        <v>-2327.364</v>
+        <v>-2294.622</v>
       </c>
       <c r="F10">
-        <v>261.936</v>
+        <v>294.678</v>
       </c>
       <c r="G10">
         <v>306.8</v>
@@ -2095,28 +2095,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M10">
-        <v>13.1753808</v>
+        <v>14.8223034</v>
       </c>
       <c r="N10">
-        <v>509.7246192000001</v>
+        <v>508.0776966000001</v>
       </c>
       <c r="O10">
-        <v>45.875215728</v>
+        <v>45.726992694</v>
       </c>
       <c r="P10">
-        <v>463.8494034720001</v>
+        <v>462.3507039060001</v>
       </c>
       <c r="Q10">
-        <v>1007.149403472</v>
+        <v>1005.650703906</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1193889125252866</v>
+        <v>0.1201301384773946</v>
       </c>
       <c r="T10">
-        <v>1.070808342605745</v>
+        <v>1.081594083365271</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>39.68765745275461</v>
+        <v>35.27791773578188</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1134379960144291</v>
+        <v>0.1133763525055945</v>
       </c>
       <c r="C11">
-        <v>3229.782418568403</v>
+        <v>3198.660581375866</v>
       </c>
       <c r="D11">
-        <v>3217.660418568402</v>
+        <v>3219.280581375865</v>
       </c>
       <c r="E11">
-        <v>-2294.622</v>
+        <v>-2261.88</v>
       </c>
       <c r="F11">
-        <v>294.678</v>
+        <v>327.42</v>
       </c>
       <c r="G11">
         <v>306.8</v>
@@ -2177,28 +2177,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M11">
-        <v>14.8223034</v>
+        <v>16.469226</v>
       </c>
       <c r="N11">
-        <v>508.0776966000001</v>
+        <v>506.4307740000001</v>
       </c>
       <c r="O11">
-        <v>45.726992694</v>
+        <v>45.57876966000001</v>
       </c>
       <c r="P11">
-        <v>462.3507039060001</v>
+        <v>460.8520043400001</v>
       </c>
       <c r="Q11">
-        <v>1005.650703906</v>
+        <v>1004.15200434</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1201301384773946</v>
+        <v>0.1208878361173273</v>
       </c>
       <c r="T11">
-        <v>1.081594083365271</v>
+        <v>1.092619507252787</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>35.27791773578188</v>
+        <v>31.7501259622037</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1133763525055945</v>
+        <v>0.11331470899676</v>
       </c>
       <c r="C12">
-        <v>3198.660581375865</v>
+        <v>3167.540376580509</v>
       </c>
       <c r="D12">
-        <v>3219.280581375865</v>
+        <v>3220.902376580509</v>
       </c>
       <c r="E12">
-        <v>-2261.88</v>
+        <v>-2229.138</v>
       </c>
       <c r="F12">
-        <v>327.4200000000001</v>
+        <v>360.162</v>
       </c>
       <c r="G12">
         <v>306.8</v>
@@ -2259,28 +2259,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M12">
-        <v>16.469226</v>
+        <v>18.1161486</v>
       </c>
       <c r="N12">
-        <v>506.4307740000001</v>
+        <v>504.7838514000001</v>
       </c>
       <c r="O12">
-        <v>45.57876966000001</v>
+        <v>45.43054662600001</v>
       </c>
       <c r="P12">
-        <v>460.8520043400001</v>
+        <v>459.3533047740001</v>
       </c>
       <c r="Q12">
-        <v>1004.15200434</v>
+        <v>1002.653304774</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1208878361173273</v>
+        <v>0.1216625606705168</v>
       </c>
       <c r="T12">
-        <v>1.092619507252787</v>
+        <v>1.103892693474853</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>31.75012596220369</v>
+        <v>28.86375087473063</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.11331470899676</v>
+        <v>0.1132530654879254</v>
       </c>
       <c r="C13">
-        <v>3167.540376580509</v>
+        <v>3136.421806650662</v>
       </c>
       <c r="D13">
-        <v>3220.902376580509</v>
+        <v>3222.525806650662</v>
       </c>
       <c r="E13">
-        <v>-2229.138</v>
+        <v>-2196.396</v>
       </c>
       <c r="F13">
-        <v>360.162</v>
+        <v>392.904</v>
       </c>
       <c r="G13">
         <v>306.8</v>
@@ -2341,28 +2341,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M13">
-        <v>18.1161486</v>
+        <v>19.7630712</v>
       </c>
       <c r="N13">
-        <v>504.7838514000001</v>
+        <v>503.1369288000001</v>
       </c>
       <c r="O13">
-        <v>45.43054662600001</v>
+        <v>45.282323592</v>
       </c>
       <c r="P13">
-        <v>459.3533047740001</v>
+        <v>457.8546052080001</v>
       </c>
       <c r="Q13">
-        <v>1002.653304774</v>
+        <v>1001.154605208</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1216625606705168</v>
+        <v>0.1224548925999153</v>
       </c>
       <c r="T13">
-        <v>1.103892693474853</v>
+        <v>1.115422088474694</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>28.86375087473063</v>
+        <v>26.45843830183641</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1132530654879254</v>
+        <v>0.1131914219790909</v>
       </c>
       <c r="C14">
-        <v>3136.421806650662</v>
+        <v>3105.304874059632</v>
       </c>
       <c r="D14">
-        <v>3222.525806650662</v>
+        <v>3224.150874059632</v>
       </c>
       <c r="E14">
-        <v>-2196.396</v>
+        <v>-2163.654</v>
       </c>
       <c r="F14">
-        <v>392.904</v>
+        <v>425.6460000000001</v>
       </c>
       <c r="G14">
         <v>306.8</v>
@@ -2423,28 +2423,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M14">
-        <v>19.7630712</v>
+        <v>21.4099938</v>
       </c>
       <c r="N14">
-        <v>503.1369288000001</v>
+        <v>501.4900062000001</v>
       </c>
       <c r="O14">
-        <v>45.282323592</v>
+        <v>45.13410055800001</v>
       </c>
       <c r="P14">
-        <v>457.8546052080001</v>
+        <v>456.3559056420001</v>
       </c>
       <c r="Q14">
-        <v>1001.154605208</v>
+        <v>999.6559056420001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1224548925999153</v>
+        <v>0.1232654390564263</v>
       </c>
       <c r="T14">
-        <v>1.115422088474694</v>
+        <v>1.127216527037749</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>26.45843830183641</v>
+        <v>24.42317381707976</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1131914219790909</v>
+        <v>0.1131297784702563</v>
       </c>
       <c r="C15">
-        <v>3105.304874059632</v>
+        <v>3074.189581285722</v>
       </c>
       <c r="D15">
-        <v>3224.150874059632</v>
+        <v>3225.777581285722</v>
       </c>
       <c r="E15">
-        <v>-2163.654</v>
+        <v>-2130.912</v>
       </c>
       <c r="F15">
-        <v>425.6460000000001</v>
+        <v>458.3880000000001</v>
       </c>
       <c r="G15">
         <v>306.8</v>
@@ -2505,28 +2505,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M15">
-        <v>21.4099938</v>
+        <v>23.0569164</v>
       </c>
       <c r="N15">
-        <v>501.4900062000001</v>
+        <v>499.8430836000001</v>
       </c>
       <c r="O15">
-        <v>45.13410055800001</v>
+        <v>44.98587752400001</v>
       </c>
       <c r="P15">
-        <v>456.3559056420001</v>
+        <v>454.8572060760001</v>
       </c>
       <c r="Q15">
-        <v>999.6559056420001</v>
+        <v>998.1572060760001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1232654390564263</v>
+        <v>0.1240948354305306</v>
       </c>
       <c r="T15">
-        <v>1.127216527037749</v>
+        <v>1.139285254869713</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>24.42317381707976</v>
+        <v>22.67866140157406</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1131297784702563</v>
+        <v>0.1130681349614218</v>
       </c>
       <c r="C16">
-        <v>3074.189581285722</v>
+        <v>3043.075930812232</v>
       </c>
       <c r="D16">
-        <v>3225.777581285722</v>
+        <v>3227.405930812232</v>
       </c>
       <c r="E16">
-        <v>-2130.912</v>
+        <v>-2098.17</v>
       </c>
       <c r="F16">
-        <v>458.3880000000001</v>
+        <v>491.1300000000001</v>
       </c>
       <c r="G16">
         <v>306.8</v>
@@ -2587,28 +2587,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M16">
-        <v>23.0569164</v>
+        <v>24.70383900000001</v>
       </c>
       <c r="N16">
-        <v>499.8430836000001</v>
+        <v>498.1961610000001</v>
       </c>
       <c r="O16">
-        <v>44.98587752400001</v>
+        <v>44.83765449000001</v>
       </c>
       <c r="P16">
-        <v>454.8572060760001</v>
+        <v>453.3585065100001</v>
       </c>
       <c r="Q16">
-        <v>998.1572060760001</v>
+        <v>996.6585065100001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1240948354305306</v>
+        <v>0.1249437470134374</v>
       </c>
       <c r="T16">
-        <v>1.139285254869713</v>
+        <v>1.151637952768311</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>22.67866140157406</v>
+        <v>21.16675064146913</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1130681349614218</v>
+        <v>0.1130064914525873</v>
       </c>
       <c r="C17">
-        <v>3043.075930812232</v>
+        <v>3011.963925127486</v>
       </c>
       <c r="D17">
-        <v>3227.405930812232</v>
+        <v>3229.035925127485</v>
       </c>
       <c r="E17">
-        <v>-2098.17</v>
+        <v>-2065.428</v>
       </c>
       <c r="F17">
-        <v>491.13</v>
+        <v>523.8720000000001</v>
       </c>
       <c r="G17">
         <v>306.8</v>
@@ -2669,28 +2669,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M17">
-        <v>24.703839</v>
+        <v>26.3507616</v>
       </c>
       <c r="N17">
-        <v>498.1961610000001</v>
+        <v>496.5492384000001</v>
       </c>
       <c r="O17">
-        <v>44.83765449000001</v>
+        <v>44.68943145600001</v>
       </c>
       <c r="P17">
-        <v>453.3585065100001</v>
+        <v>451.8598069440001</v>
       </c>
       <c r="Q17">
-        <v>996.6585065100001</v>
+        <v>995.159806944</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1249437470134374</v>
+        <v>0.1258128707768896</v>
       </c>
       <c r="T17">
-        <v>1.151637952768311</v>
+        <v>1.164284762521638</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>21.16675064146913</v>
+        <v>19.84382872637731</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1130064914525873</v>
+        <v>0.1129448479437527</v>
       </c>
       <c r="C18">
-        <v>3011.963925127486</v>
+        <v>2980.853566724832</v>
       </c>
       <c r="D18">
-        <v>3229.035925127485</v>
+        <v>3230.667566724832</v>
       </c>
       <c r="E18">
-        <v>-2065.428</v>
+        <v>-2032.686</v>
       </c>
       <c r="F18">
-        <v>523.8720000000001</v>
+        <v>556.614</v>
       </c>
       <c r="G18">
         <v>306.8</v>
@@ -2751,28 +2751,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M18">
-        <v>26.3507616</v>
+        <v>27.9976842</v>
       </c>
       <c r="N18">
-        <v>496.5492384000001</v>
+        <v>494.9023158000001</v>
       </c>
       <c r="O18">
-        <v>44.68943145600001</v>
+        <v>44.54120842200001</v>
       </c>
       <c r="P18">
-        <v>451.8598069440001</v>
+        <v>450.3611073780001</v>
       </c>
       <c r="Q18">
-        <v>995.159806944</v>
+        <v>993.661107378</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1258128707768896</v>
+        <v>0.1267029372816298</v>
       </c>
       <c r="T18">
-        <v>1.164284762521638</v>
+        <v>1.177236314678659</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>19.84382872637731</v>
+        <v>18.67654468364923</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1129448479437527</v>
+        <v>0.1128832044349182</v>
       </c>
       <c r="C19">
-        <v>2980.853566724832</v>
+        <v>2949.744858102663</v>
       </c>
       <c r="D19">
-        <v>3230.667566724832</v>
+        <v>3232.300858102663</v>
       </c>
       <c r="E19">
-        <v>-2032.686</v>
+        <v>-1999.944</v>
       </c>
       <c r="F19">
-        <v>556.614</v>
+        <v>589.3560000000001</v>
       </c>
       <c r="G19">
         <v>306.8</v>
@@ -2833,28 +2833,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M19">
-        <v>27.9976842</v>
+        <v>29.64460680000001</v>
       </c>
       <c r="N19">
-        <v>494.9023158000001</v>
+        <v>493.2553932000001</v>
       </c>
       <c r="O19">
-        <v>44.54120842200001</v>
+        <v>44.39298538800001</v>
       </c>
       <c r="P19">
-        <v>450.3611073780001</v>
+        <v>448.8624078120001</v>
       </c>
       <c r="Q19">
-        <v>993.661107378</v>
+        <v>992.1624078120001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1267029372816298</v>
+        <v>0.1276147127255099</v>
       </c>
       <c r="T19">
-        <v>1.177236314678659</v>
+        <v>1.190503758351705</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.67654468364923</v>
+        <v>17.63895886789094</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1128832044349182</v>
+        <v>0.1128215609260836</v>
       </c>
       <c r="C20">
-        <v>2949.744858102663</v>
+        <v>2918.637801764427</v>
       </c>
       <c r="D20">
-        <v>3232.300858102662</v>
+        <v>3233.935801764426</v>
       </c>
       <c r="E20">
-        <v>-1999.944</v>
+        <v>-1967.202</v>
       </c>
       <c r="F20">
-        <v>589.356</v>
+        <v>622.0980000000001</v>
       </c>
       <c r="G20">
         <v>306.8</v>
@@ -2915,28 +2915,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M20">
-        <v>29.6446068</v>
+        <v>31.2915294</v>
       </c>
       <c r="N20">
-        <v>493.2553932000001</v>
+        <v>491.6084706000001</v>
       </c>
       <c r="O20">
-        <v>44.39298538800001</v>
+        <v>44.24476235400001</v>
       </c>
       <c r="P20">
-        <v>448.8624078120001</v>
+        <v>447.3637082460001</v>
       </c>
       <c r="Q20">
-        <v>992.1624078120001</v>
+        <v>990.6637082460001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1276147127255099</v>
+        <v>0.1285490011433131</v>
       </c>
       <c r="T20">
-        <v>1.190503758351705</v>
+        <v>1.204098793226555</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.63895886789094</v>
+        <v>16.71059261168615</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1128215609260836</v>
+        <v>0.1127599174172491</v>
       </c>
       <c r="C21">
-        <v>2918.637801764427</v>
+        <v>2887.532400218637</v>
       </c>
       <c r="D21">
-        <v>3233.935801764426</v>
+        <v>3235.572400218637</v>
       </c>
       <c r="E21">
-        <v>-1967.202</v>
+        <v>-1934.46</v>
       </c>
       <c r="F21">
-        <v>622.0980000000001</v>
+        <v>654.8400000000001</v>
       </c>
       <c r="G21">
         <v>306.8</v>
@@ -2997,28 +2997,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M21">
-        <v>31.2915294</v>
+        <v>32.93845200000001</v>
       </c>
       <c r="N21">
-        <v>491.6084706000001</v>
+        <v>489.9615480000001</v>
       </c>
       <c r="O21">
-        <v>44.24476235400001</v>
+        <v>44.09653932000001</v>
       </c>
       <c r="P21">
-        <v>447.3637082460001</v>
+        <v>445.8650086800001</v>
       </c>
       <c r="Q21">
-        <v>990.6637082460001</v>
+        <v>989.16500868</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1285490011433131</v>
+        <v>0.1295066467715613</v>
       </c>
       <c r="T21">
-        <v>1.204098793226555</v>
+        <v>1.218033703973276</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.71059261168615</v>
+        <v>15.87506298110184</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1127599174172491</v>
+        <v>0.1126982739084145</v>
       </c>
       <c r="C22">
-        <v>2887.532400218637</v>
+        <v>2856.42865597889</v>
       </c>
       <c r="D22">
-        <v>3235.572400218637</v>
+        <v>3237.21065597889</v>
       </c>
       <c r="E22">
-        <v>-1934.46</v>
+        <v>-1901.718</v>
       </c>
       <c r="F22">
-        <v>654.8400000000001</v>
+        <v>687.5820000000001</v>
       </c>
       <c r="G22">
         <v>306.8</v>
@@ -3079,28 +3079,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M22">
-        <v>32.93845200000001</v>
+        <v>34.5853746</v>
       </c>
       <c r="N22">
-        <v>489.9615480000001</v>
+        <v>488.3146254000001</v>
       </c>
       <c r="O22">
-        <v>44.09653932000001</v>
+        <v>43.94831628600001</v>
       </c>
       <c r="P22">
-        <v>445.8650086800001</v>
+        <v>444.366309114</v>
       </c>
       <c r="Q22">
-        <v>989.16500868</v>
+        <v>987.666309114</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1295066467715613</v>
+        <v>0.1304885365929298</v>
       </c>
       <c r="T22">
-        <v>1.218033703973276</v>
+        <v>1.232321397270547</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.87506298110184</v>
+        <v>15.11910760104938</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1126982739084145</v>
+        <v>0.11263663039958</v>
       </c>
       <c r="C23">
-        <v>2856.42865597889</v>
+        <v>2825.326571563874</v>
       </c>
       <c r="D23">
-        <v>3237.21065597889</v>
+        <v>3238.850571563874</v>
       </c>
       <c r="E23">
-        <v>-1901.718</v>
+        <v>-1868.976</v>
       </c>
       <c r="F23">
-        <v>687.582</v>
+        <v>720.3240000000001</v>
       </c>
       <c r="G23">
         <v>306.8</v>
@@ -3161,28 +3161,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M23">
-        <v>34.58537459999999</v>
+        <v>36.2322972</v>
       </c>
       <c r="N23">
-        <v>488.3146254000001</v>
+        <v>486.6677028000001</v>
       </c>
       <c r="O23">
-        <v>43.94831628600001</v>
+        <v>43.800093252</v>
       </c>
       <c r="P23">
-        <v>444.366309114</v>
+        <v>442.8676095480001</v>
       </c>
       <c r="Q23">
-        <v>987.666309114</v>
+        <v>986.167609548</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1304885365929298</v>
+        <v>0.1314956030763846</v>
       </c>
       <c r="T23">
-        <v>1.232321397270547</v>
+        <v>1.246975441678004</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.11910760104938</v>
+        <v>14.43187543736531</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.11263663039958</v>
+        <v>0.1125749868907454</v>
       </c>
       <c r="C24">
-        <v>2825.326571563874</v>
+        <v>2794.226149497385</v>
       </c>
       <c r="D24">
-        <v>3238.850571563874</v>
+        <v>3240.492149497385</v>
       </c>
       <c r="E24">
-        <v>-1868.976</v>
+        <v>-1836.234</v>
       </c>
       <c r="F24">
-        <v>720.3240000000001</v>
+        <v>753.0660000000001</v>
       </c>
       <c r="G24">
         <v>306.8</v>
@@ -3243,28 +3243,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M24">
-        <v>36.2322972</v>
+        <v>37.87921980000001</v>
       </c>
       <c r="N24">
-        <v>486.6677028000001</v>
+        <v>485.0207802000001</v>
       </c>
       <c r="O24">
-        <v>43.800093252</v>
+        <v>43.65187021800001</v>
       </c>
       <c r="P24">
-        <v>442.8676095480001</v>
+        <v>441.3689099820001</v>
       </c>
       <c r="Q24">
-        <v>986.167609548</v>
+        <v>984.6689099820001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1314956030763846</v>
+        <v>0.1325288271308382</v>
       </c>
       <c r="T24">
-        <v>1.246975441678004</v>
+        <v>1.262010110615525</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.43187543736531</v>
+        <v>13.80440259226247</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1125749868907454</v>
+        <v>0.1125133433819109</v>
       </c>
       <c r="C25">
-        <v>2794.226149497385</v>
+        <v>2763.127392308335</v>
       </c>
       <c r="D25">
-        <v>3240.492149497385</v>
+        <v>3242.135392308335</v>
       </c>
       <c r="E25">
-        <v>-1836.234</v>
+        <v>-1803.492</v>
       </c>
       <c r="F25">
-        <v>753.0660000000001</v>
+        <v>785.8080000000001</v>
       </c>
       <c r="G25">
         <v>306.8</v>
@@ -3325,28 +3325,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M25">
-        <v>37.87921980000001</v>
+        <v>39.5261424</v>
       </c>
       <c r="N25">
-        <v>485.0207802000001</v>
+        <v>483.3738576000001</v>
       </c>
       <c r="O25">
-        <v>43.65187021800001</v>
+        <v>43.503647184</v>
       </c>
       <c r="P25">
-        <v>441.3689099820001</v>
+        <v>439.8702104160001</v>
       </c>
       <c r="Q25">
-        <v>984.6689099820001</v>
+        <v>983.170210416</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1325288271308382</v>
+        <v>0.133589241291988</v>
       </c>
       <c r="T25">
-        <v>1.262010110615525</v>
+        <v>1.277440428735613</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>13.80440259226247</v>
+        <v>13.2292191509182</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1125133433819109</v>
+        <v>0.1127929498730763</v>
       </c>
       <c r="C26">
-        <v>2763.127392308335</v>
+        <v>2722.945202248097</v>
       </c>
       <c r="D26">
-        <v>3242.135392308335</v>
+        <v>3234.695202248097</v>
       </c>
       <c r="E26">
-        <v>-1803.492</v>
+        <v>-1770.75</v>
       </c>
       <c r="F26">
-        <v>785.808</v>
+        <v>818.5500000000001</v>
       </c>
       <c r="G26">
         <v>306.8</v>
@@ -3407,45 +3407,45 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M26">
-        <v>39.5261424</v>
+        <v>42.40089</v>
       </c>
       <c r="N26">
-        <v>483.3738576000001</v>
+        <v>480.4991100000001</v>
       </c>
       <c r="O26">
-        <v>43.503647184</v>
+        <v>43.24491990000001</v>
       </c>
       <c r="P26">
-        <v>439.8702104160001</v>
+        <v>437.2541901000001</v>
       </c>
       <c r="Q26">
-        <v>983.170210416</v>
+        <v>980.5541901</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.133589241291988</v>
+        <v>0.1346779331641018</v>
       </c>
       <c r="T26">
-        <v>1.277440428735612</v>
+        <v>1.293282222005569</v>
       </c>
       <c r="U26">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.09</v>
       </c>
       <c r="W26">
-        <v>0.045773</v>
+        <v>0.047138</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>13.22921915091821</v>
+        <v>12.33228830809919</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1127929498730763</v>
+        <v>0.1127449563642418</v>
       </c>
       <c r="C27">
-        <v>2722.945202248097</v>
+        <v>2691.477857099634</v>
       </c>
       <c r="D27">
-        <v>3234.695202248097</v>
+        <v>3235.969857099634</v>
       </c>
       <c r="E27">
-        <v>-1770.75</v>
+        <v>-1738.008</v>
       </c>
       <c r="F27">
-        <v>818.5500000000001</v>
+        <v>851.2920000000001</v>
       </c>
       <c r="G27">
         <v>306.8</v>
@@ -3489,28 +3489,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M27">
-        <v>42.40089</v>
+        <v>44.09692560000001</v>
       </c>
       <c r="N27">
-        <v>480.4991100000001</v>
+        <v>478.8030744000001</v>
       </c>
       <c r="O27">
-        <v>43.24491990000001</v>
+        <v>43.09227669600001</v>
       </c>
       <c r="P27">
-        <v>437.2541901000001</v>
+        <v>435.7107977040001</v>
       </c>
       <c r="Q27">
-        <v>980.5541901</v>
+        <v>979.010797704</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1346779331641018</v>
+        <v>0.1357960491408673</v>
       </c>
       <c r="T27">
-        <v>1.293282222005569</v>
+        <v>1.309552171850389</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>12.33228830809919</v>
+        <v>11.85796952701845</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1127449563642418</v>
+        <v>0.1126969628554073</v>
       </c>
       <c r="C28">
-        <v>2691.477857099634</v>
+        <v>2660.011516920965</v>
       </c>
       <c r="D28">
-        <v>3235.969857099634</v>
+        <v>3237.245516920965</v>
       </c>
       <c r="E28">
-        <v>-1738.008</v>
+        <v>-1705.266</v>
       </c>
       <c r="F28">
-        <v>851.2920000000001</v>
+        <v>884.0340000000001</v>
       </c>
       <c r="G28">
         <v>306.8</v>
@@ -3571,28 +3571,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M28">
-        <v>44.09692560000001</v>
+        <v>45.79296120000001</v>
       </c>
       <c r="N28">
-        <v>478.8030744000001</v>
+        <v>477.1070388000001</v>
       </c>
       <c r="O28">
-        <v>43.09227669600001</v>
+        <v>42.93963349200001</v>
       </c>
       <c r="P28">
-        <v>435.7107977040001</v>
+        <v>434.1674053080001</v>
       </c>
       <c r="Q28">
-        <v>979.010797704</v>
+        <v>977.467405308</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1357960491408673</v>
+        <v>0.1369447984320647</v>
       </c>
       <c r="T28">
-        <v>1.309552171850389</v>
+        <v>1.326267873745752</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.85796952701845</v>
+        <v>11.41878547046221</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1126969628554073</v>
+        <v>0.1126489693465727</v>
       </c>
       <c r="C29">
-        <v>2660.011516920965</v>
+        <v>2628.546182901074</v>
       </c>
       <c r="D29">
-        <v>3237.245516920965</v>
+        <v>3238.522182901074</v>
       </c>
       <c r="E29">
-        <v>-1705.266</v>
+        <v>-1672.524</v>
       </c>
       <c r="F29">
-        <v>884.0340000000001</v>
+        <v>916.7760000000002</v>
       </c>
       <c r="G29">
         <v>306.8</v>
@@ -3653,28 +3653,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M29">
-        <v>45.79296120000001</v>
+        <v>47.48899680000001</v>
       </c>
       <c r="N29">
-        <v>477.1070388000001</v>
+        <v>475.4110032000001</v>
       </c>
       <c r="O29">
-        <v>42.93963349200001</v>
+        <v>42.78699028800001</v>
       </c>
       <c r="P29">
-        <v>434.1674053080001</v>
+        <v>432.6240129120001</v>
       </c>
       <c r="Q29">
-        <v>977.467405308</v>
+        <v>975.9240129120001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1369447984320647</v>
+        <v>0.1381254574257954</v>
       </c>
       <c r="T29">
-        <v>1.326267873745752</v>
+        <v>1.343447900693765</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.41878547046221</v>
+        <v>11.01097170365999</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1126489693465727</v>
+        <v>0.1126009758377382</v>
       </c>
       <c r="C30">
-        <v>2628.546182901074</v>
+        <v>2597.08185623082</v>
       </c>
       <c r="D30">
-        <v>3238.522182901074</v>
+        <v>3239.799856230819</v>
       </c>
       <c r="E30">
-        <v>-1672.524</v>
+        <v>-1639.782</v>
       </c>
       <c r="F30">
-        <v>916.7760000000002</v>
+        <v>949.5180000000001</v>
       </c>
       <c r="G30">
         <v>306.8</v>
@@ -3735,28 +3735,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M30">
-        <v>47.48899680000001</v>
+        <v>49.1850324</v>
       </c>
       <c r="N30">
-        <v>475.4110032000001</v>
+        <v>473.7149676000001</v>
       </c>
       <c r="O30">
-        <v>42.78699028800001</v>
+        <v>42.63434708400001</v>
       </c>
       <c r="P30">
-        <v>432.6240129120001</v>
+        <v>431.0806205160001</v>
       </c>
       <c r="Q30">
-        <v>975.9240129120001</v>
+        <v>974.380620516</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1381254574257954</v>
+        <v>0.1393393744193495</v>
       </c>
       <c r="T30">
-        <v>1.343447900693765</v>
+        <v>1.361111872062848</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.01097170365999</v>
+        <v>10.63128302422344</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1126009758377381</v>
+        <v>0.1125529823289036</v>
       </c>
       <c r="C31">
-        <v>2597.08185623082</v>
+        <v>2565.618538102944</v>
       </c>
       <c r="D31">
-        <v>3239.79985623082</v>
+        <v>3241.078538102944</v>
       </c>
       <c r="E31">
-        <v>-1639.782</v>
+        <v>-1607.04</v>
       </c>
       <c r="F31">
-        <v>949.518</v>
+        <v>982.26</v>
       </c>
       <c r="G31">
         <v>306.8</v>
@@ -3817,28 +3817,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M31">
-        <v>49.1850324</v>
+        <v>50.881068</v>
       </c>
       <c r="N31">
-        <v>473.7149676000001</v>
+        <v>472.0189320000001</v>
       </c>
       <c r="O31">
-        <v>42.63434708400001</v>
+        <v>42.48170388</v>
       </c>
       <c r="P31">
-        <v>431.0806205160001</v>
+        <v>429.5372281200001</v>
       </c>
       <c r="Q31">
-        <v>974.380620516</v>
+        <v>972.83722812</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1393393744193495</v>
+        <v>0.1405879747555766</v>
       </c>
       <c r="T31">
-        <v>1.361111872062847</v>
+        <v>1.37928052832819</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.63128302422344</v>
+        <v>10.276906923416</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1125529823289036</v>
+        <v>0.112504988820069</v>
       </c>
       <c r="C32">
-        <v>2565.618538102944</v>
+        <v>2534.15622971207</v>
       </c>
       <c r="D32">
-        <v>3241.078538102944</v>
+        <v>3242.35822971207</v>
       </c>
       <c r="E32">
-        <v>-1607.04</v>
+        <v>-1574.298</v>
       </c>
       <c r="F32">
-        <v>982.26</v>
+        <v>1015.002</v>
       </c>
       <c r="G32">
         <v>306.8</v>
@@ -3899,28 +3899,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M32">
-        <v>50.881068</v>
+        <v>52.5771036</v>
       </c>
       <c r="N32">
-        <v>472.0189320000001</v>
+        <v>470.3228964000001</v>
       </c>
       <c r="O32">
-        <v>42.48170388</v>
+        <v>42.329060676</v>
       </c>
       <c r="P32">
-        <v>429.5372281200001</v>
+        <v>427.9938357240001</v>
       </c>
       <c r="Q32">
-        <v>972.83722812</v>
+        <v>971.293835724</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1405879747555766</v>
+        <v>0.1418727664058972</v>
       </c>
       <c r="T32">
-        <v>1.37928052832819</v>
+        <v>1.397975812311368</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.276906923416</v>
+        <v>9.945393796854189</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.112504988820069</v>
+        <v>0.1129520353112345</v>
       </c>
       <c r="C33">
-        <v>2534.15622971207</v>
+        <v>2489.533239429328</v>
       </c>
       <c r="D33">
-        <v>3242.35822971207</v>
+        <v>3230.477239429328</v>
       </c>
       <c r="E33">
-        <v>-1574.298</v>
+        <v>-1541.556</v>
       </c>
       <c r="F33">
-        <v>1015.002</v>
+        <v>1047.744</v>
       </c>
       <c r="G33">
         <v>306.8</v>
@@ -3981,45 +3981,45 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M33">
-        <v>52.5771036</v>
+        <v>56.05430400000001</v>
       </c>
       <c r="N33">
-        <v>470.3228964000001</v>
+        <v>466.8456960000001</v>
       </c>
       <c r="O33">
-        <v>42.329060676</v>
+        <v>42.01611264000001</v>
       </c>
       <c r="P33">
-        <v>427.9938357240001</v>
+        <v>424.8295833600001</v>
       </c>
       <c r="Q33">
-        <v>971.293835724</v>
+        <v>968.12958336</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1418727664058972</v>
+        <v>0.1431953460459331</v>
       </c>
       <c r="T33">
-        <v>1.397975812311368</v>
+        <v>1.41722095758817</v>
       </c>
       <c r="U33">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V33">
         <v>0.09</v>
       </c>
       <c r="W33">
-        <v>0.047138</v>
+        <v>0.048685</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>9.945393796854189</v>
+        <v>9.328454064829705</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1129520353112345</v>
+        <v>0.1129195118024</v>
       </c>
       <c r="C34">
-        <v>2489.533239429328</v>
+        <v>2457.652667115118</v>
       </c>
       <c r="D34">
-        <v>3230.477239429328</v>
+        <v>3231.338667115117</v>
       </c>
       <c r="E34">
-        <v>-1541.556</v>
+        <v>-1508.814</v>
       </c>
       <c r="F34">
-        <v>1047.744</v>
+        <v>1080.486</v>
       </c>
       <c r="G34">
         <v>306.8</v>
@@ -4063,28 +4063,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M34">
-        <v>56.05430400000001</v>
+        <v>57.806001</v>
       </c>
       <c r="N34">
-        <v>466.8456960000001</v>
+        <v>465.0939990000001</v>
       </c>
       <c r="O34">
-        <v>42.01611264000001</v>
+        <v>41.85845991000001</v>
       </c>
       <c r="P34">
-        <v>424.8295833600001</v>
+        <v>423.2355390900001</v>
       </c>
       <c r="Q34">
-        <v>968.12958336</v>
+        <v>966.53553909</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1431953460459331</v>
+        <v>0.1445574056752238</v>
       </c>
       <c r="T34">
-        <v>1.41722095758817</v>
+        <v>1.437040584813532</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.328454064829705</v>
+        <v>9.045773638622746</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1129195118024</v>
+        <v>0.1128869882935654</v>
       </c>
       <c r="C35">
-        <v>2457.652667115118</v>
+        <v>2425.772554333991</v>
       </c>
       <c r="D35">
-        <v>3231.338667115117</v>
+        <v>3232.200554333991</v>
       </c>
       <c r="E35">
-        <v>-1508.814</v>
+        <v>-1476.072</v>
       </c>
       <c r="F35">
-        <v>1080.486</v>
+        <v>1113.228</v>
       </c>
       <c r="G35">
         <v>306.8</v>
@@ -4145,28 +4145,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M35">
-        <v>57.806001</v>
+        <v>59.557698</v>
       </c>
       <c r="N35">
-        <v>465.0939990000001</v>
+        <v>463.3423020000001</v>
       </c>
       <c r="O35">
-        <v>41.85845991000001</v>
+        <v>41.70080718000001</v>
       </c>
       <c r="P35">
-        <v>423.2355390900001</v>
+        <v>421.64149482</v>
       </c>
       <c r="Q35">
-        <v>966.53553909</v>
+        <v>964.94149482</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1445574056752238</v>
+        <v>0.1459607398387355</v>
       </c>
       <c r="T35">
-        <v>1.437040584813532</v>
+        <v>1.4574608068033</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.045773638622746</v>
+        <v>8.779721472780899</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1128869882935654</v>
+        <v>0.1128544647847309</v>
       </c>
       <c r="C36">
-        <v>2425.772554333991</v>
+        <v>2393.892901453757</v>
       </c>
       <c r="D36">
-        <v>3232.200554333991</v>
+        <v>3233.062901453757</v>
       </c>
       <c r="E36">
-        <v>-1476.072</v>
+        <v>-1443.33</v>
       </c>
       <c r="F36">
-        <v>1113.228</v>
+        <v>1145.97</v>
       </c>
       <c r="G36">
         <v>306.8</v>
@@ -4227,28 +4227,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M36">
-        <v>59.557698</v>
+        <v>61.30939500000001</v>
       </c>
       <c r="N36">
-        <v>463.3423020000001</v>
+        <v>461.5906050000001</v>
       </c>
       <c r="O36">
-        <v>41.70080718000001</v>
+        <v>41.54315445000001</v>
       </c>
       <c r="P36">
-        <v>421.64149482</v>
+        <v>420.0474505500001</v>
       </c>
       <c r="Q36">
-        <v>964.94149482</v>
+        <v>963.3474505500001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1459607398387355</v>
+        <v>0.1474072535149706</v>
       </c>
       <c r="T36">
-        <v>1.4574608068033</v>
+        <v>1.47850934331583</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.779721472780899</v>
+        <v>8.528872287844301</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1128544647847309</v>
+        <v>0.1128219412758963</v>
       </c>
       <c r="C37">
-        <v>2393.892901453757</v>
+        <v>2362.013708842618</v>
       </c>
       <c r="D37">
-        <v>3233.062901453757</v>
+        <v>3233.925708842618</v>
       </c>
       <c r="E37">
-        <v>-1443.33</v>
+        <v>-1410.588</v>
       </c>
       <c r="F37">
-        <v>1145.97</v>
+        <v>1178.712</v>
       </c>
       <c r="G37">
         <v>306.8</v>
@@ -4309,28 +4309,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M37">
-        <v>61.30939500000001</v>
+        <v>63.06109200000001</v>
       </c>
       <c r="N37">
-        <v>461.5906050000001</v>
+        <v>459.8389080000001</v>
       </c>
       <c r="O37">
-        <v>41.54315445000001</v>
+        <v>41.38550172</v>
       </c>
       <c r="P37">
-        <v>420.0474505500001</v>
+        <v>418.4534062800001</v>
       </c>
       <c r="Q37">
-        <v>963.3474505500001</v>
+        <v>961.75340628</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1474072535149706</v>
+        <v>0.148898970743588</v>
       </c>
       <c r="T37">
-        <v>1.47850934331583</v>
+        <v>1.500215646594376</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.528872287844301</v>
+        <v>8.291959168737517</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1128219412758963</v>
+        <v>0.1127894177670618</v>
       </c>
       <c r="C38">
-        <v>2362.013708842618</v>
+        <v>2330.134976869168</v>
       </c>
       <c r="D38">
-        <v>3233.925708842618</v>
+        <v>3234.788976869168</v>
       </c>
       <c r="E38">
-        <v>-1410.588</v>
+        <v>-1377.846</v>
       </c>
       <c r="F38">
-        <v>1178.712</v>
+        <v>1211.454</v>
       </c>
       <c r="G38">
         <v>306.8</v>
@@ -4391,28 +4391,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M38">
-        <v>63.061092</v>
+        <v>64.81278900000001</v>
       </c>
       <c r="N38">
-        <v>459.8389080000001</v>
+        <v>458.0872110000001</v>
       </c>
       <c r="O38">
-        <v>41.38550172000001</v>
+        <v>41.22784899000001</v>
       </c>
       <c r="P38">
-        <v>418.4534062800001</v>
+        <v>416.8593620100001</v>
       </c>
       <c r="Q38">
-        <v>961.75340628</v>
+        <v>960.15936201</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.148898970743588</v>
+        <v>0.1504380440747012</v>
       </c>
       <c r="T38">
-        <v>1.500215646594376</v>
+        <v>1.522611038865892</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.291959168737518</v>
+        <v>8.067852164177044</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1127894177670618</v>
+        <v>0.1127568942582272</v>
       </c>
       <c r="C39">
-        <v>2330.134976869168</v>
+        <v>2298.256705902395</v>
       </c>
       <c r="D39">
-        <v>3234.788976869168</v>
+        <v>3235.652705902395</v>
       </c>
       <c r="E39">
-        <v>-1377.846</v>
+        <v>-1345.104</v>
       </c>
       <c r="F39">
-        <v>1211.454</v>
+        <v>1244.196</v>
       </c>
       <c r="G39">
         <v>306.8</v>
@@ -4473,28 +4473,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M39">
-        <v>64.81278900000001</v>
+        <v>66.564486</v>
       </c>
       <c r="N39">
-        <v>458.0872110000001</v>
+        <v>456.3355140000001</v>
       </c>
       <c r="O39">
-        <v>41.22784899000001</v>
+        <v>41.07019626000001</v>
       </c>
       <c r="P39">
-        <v>416.8593620100001</v>
+        <v>415.2653177400001</v>
       </c>
       <c r="Q39">
-        <v>960.15936201</v>
+        <v>958.5653177400001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1504380440747012</v>
+        <v>0.1520267649326246</v>
       </c>
       <c r="T39">
-        <v>1.522611038865892</v>
+        <v>1.545728863146166</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.067852164177044</v>
+        <v>7.855540265119753</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1127568942582272</v>
+        <v>0.1127243707493927</v>
       </c>
       <c r="C40">
-        <v>2298.256705902395</v>
+        <v>2266.37889631168</v>
       </c>
       <c r="D40">
-        <v>3235.652705902395</v>
+        <v>3236.51689631168</v>
       </c>
       <c r="E40">
-        <v>-1345.104</v>
+        <v>-1312.362</v>
       </c>
       <c r="F40">
-        <v>1244.196</v>
+        <v>1276.938</v>
       </c>
       <c r="G40">
         <v>306.8</v>
@@ -4555,28 +4555,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M40">
-        <v>66.564486</v>
+        <v>68.31618300000001</v>
       </c>
       <c r="N40">
-        <v>456.3355140000001</v>
+        <v>454.5838170000001</v>
       </c>
       <c r="O40">
-        <v>41.07019626000001</v>
+        <v>40.91254353000001</v>
       </c>
       <c r="P40">
-        <v>415.2653177400001</v>
+        <v>413.6712734700001</v>
       </c>
       <c r="Q40">
-        <v>958.5653177400001</v>
+        <v>956.97127347</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1520267649326246</v>
+        <v>0.1536675749990044</v>
       </c>
       <c r="T40">
-        <v>1.545728863146166</v>
+        <v>1.569604648878253</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.855540265119753</v>
+        <v>7.654116155757706</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1127243707493927</v>
+        <v>0.1129830472405582</v>
       </c>
       <c r="C41">
-        <v>2266.37889631168</v>
+        <v>2226.776275560907</v>
       </c>
       <c r="D41">
-        <v>3236.51689631168</v>
+        <v>3229.656275560907</v>
       </c>
       <c r="E41">
-        <v>-1312.362</v>
+        <v>-1279.62</v>
       </c>
       <c r="F41">
-        <v>1276.938</v>
+        <v>1309.68</v>
       </c>
       <c r="G41">
         <v>306.8</v>
@@ -4637,45 +4637,45 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M41">
-        <v>68.31618300000001</v>
+        <v>71.11562400000001</v>
       </c>
       <c r="N41">
-        <v>454.5838170000001</v>
+        <v>451.7843760000001</v>
       </c>
       <c r="O41">
-        <v>40.91254353000001</v>
+        <v>40.66059384</v>
       </c>
       <c r="P41">
-        <v>413.6712734700001</v>
+        <v>411.1237821600001</v>
       </c>
       <c r="Q41">
-        <v>956.97127347</v>
+        <v>954.42378216</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1536675749990044</v>
+        <v>0.1553630787342636</v>
       </c>
       <c r="T41">
-        <v>1.569604648878253</v>
+        <v>1.594276294134743</v>
       </c>
       <c r="U41">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V41">
         <v>0.09</v>
       </c>
       <c r="W41">
-        <v>0.048685</v>
+        <v>0.04941300000000001</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y41">
-        <v>7.654116155757706</v>
+        <v>7.352814622002051</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1129830472405582</v>
+        <v>0.1129578037317236</v>
       </c>
       <c r="C42">
-        <v>2226.776275560907</v>
+        <v>2194.702503216876</v>
       </c>
       <c r="D42">
-        <v>3229.656275560907</v>
+        <v>3230.324503216876</v>
       </c>
       <c r="E42">
-        <v>-1279.62</v>
+        <v>-1246.878</v>
       </c>
       <c r="F42">
-        <v>1309.68</v>
+        <v>1342.422</v>
       </c>
       <c r="G42">
         <v>306.8</v>
@@ -4719,28 +4719,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M42">
-        <v>71.11562400000001</v>
+        <v>72.89351460000002</v>
       </c>
       <c r="N42">
-        <v>451.7843760000001</v>
+        <v>450.0064854000001</v>
       </c>
       <c r="O42">
-        <v>40.66059384</v>
+        <v>40.50058368600001</v>
       </c>
       <c r="P42">
-        <v>411.1237821600001</v>
+        <v>409.5059017140001</v>
       </c>
       <c r="Q42">
-        <v>954.42378216</v>
+        <v>952.805901714</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1553630787342636</v>
+        <v>0.1571160571724129</v>
       </c>
       <c r="T42">
-        <v>1.594276294134743</v>
+        <v>1.619784266349079</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.352814622002051</v>
+        <v>7.173477680002001</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1129578037317236</v>
+        <v>0.1129325602228891</v>
       </c>
       <c r="C43">
-        <v>2194.702503216876</v>
+        <v>2162.629007447546</v>
       </c>
       <c r="D43">
-        <v>3230.324503216876</v>
+        <v>3230.993007447546</v>
       </c>
       <c r="E43">
-        <v>-1246.878</v>
+        <v>-1214.136</v>
       </c>
       <c r="F43">
-        <v>1342.422</v>
+        <v>1375.164</v>
       </c>
       <c r="G43">
         <v>306.8</v>
@@ -4801,28 +4801,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M43">
-        <v>72.89351460000002</v>
+        <v>74.67140520000001</v>
       </c>
       <c r="N43">
-        <v>450.0064854000001</v>
+        <v>448.2285948000001</v>
       </c>
       <c r="O43">
-        <v>40.50058368600001</v>
+        <v>40.34057353200001</v>
       </c>
       <c r="P43">
-        <v>409.5059017140001</v>
+        <v>407.8880212680001</v>
       </c>
       <c r="Q43">
-        <v>952.805901714</v>
+        <v>951.1880212680001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1571160571724129</v>
+        <v>0.1589294831429122</v>
       </c>
       <c r="T43">
-        <v>1.619784266349079</v>
+        <v>1.646171823812186</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.173477680002001</v>
+        <v>7.002680592382907</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1129325602228891</v>
+        <v>0.1129073167140545</v>
       </c>
       <c r="C44">
-        <v>2162.629007447546</v>
+        <v>2130.555788424659</v>
       </c>
       <c r="D44">
-        <v>3230.993007447545</v>
+        <v>3231.661788424659</v>
       </c>
       <c r="E44">
-        <v>-1214.136</v>
+        <v>-1181.394</v>
       </c>
       <c r="F44">
-        <v>1375.164</v>
+        <v>1407.906</v>
       </c>
       <c r="G44">
         <v>306.8</v>
@@ -4883,28 +4883,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M44">
-        <v>74.6714052</v>
+        <v>76.44929580000002</v>
       </c>
       <c r="N44">
-        <v>448.2285948000001</v>
+        <v>446.4507042000001</v>
       </c>
       <c r="O44">
-        <v>40.34057353200001</v>
+        <v>40.180563378</v>
       </c>
       <c r="P44">
-        <v>407.8880212680001</v>
+        <v>406.2701408220001</v>
       </c>
       <c r="Q44">
-        <v>951.1880212680001</v>
+        <v>949.570140822</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1589294831429122</v>
+        <v>0.1608065380948325</v>
       </c>
       <c r="T44">
-        <v>1.646171823812186</v>
+        <v>1.673485260484525</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.002680592382908</v>
+        <v>6.839827555350745</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1129073167140545</v>
+        <v>0.11288207320522</v>
       </c>
       <c r="C45">
-        <v>2130.555788424659</v>
+        <v>2098.482846320102</v>
       </c>
       <c r="D45">
-        <v>3231.661788424659</v>
+        <v>3232.330846320102</v>
       </c>
       <c r="E45">
-        <v>-1181.394</v>
+        <v>-1148.652</v>
       </c>
       <c r="F45">
-        <v>1407.906</v>
+        <v>1440.648</v>
       </c>
       <c r="G45">
         <v>306.8</v>
@@ -4965,28 +4965,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M45">
-        <v>76.44929580000002</v>
+        <v>78.22718640000001</v>
       </c>
       <c r="N45">
-        <v>446.4507042000001</v>
+        <v>444.6728136000001</v>
       </c>
       <c r="O45">
-        <v>40.180563378</v>
+        <v>40.020553224</v>
       </c>
       <c r="P45">
-        <v>406.2701408220001</v>
+        <v>404.6522603760001</v>
       </c>
       <c r="Q45">
-        <v>949.570140822</v>
+        <v>947.952260376</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1608065380948325</v>
+        <v>0.1627506307236071</v>
       </c>
       <c r="T45">
-        <v>1.673485260484525</v>
+        <v>1.701774177038018</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.839827555350745</v>
+        <v>6.684376929092775</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.11288207320522</v>
+        <v>0.1128568296963854</v>
       </c>
       <c r="C46">
-        <v>2098.482846320102</v>
+        <v>2066.410181305903</v>
       </c>
       <c r="D46">
-        <v>3232.330846320102</v>
+        <v>3233.000181305903</v>
       </c>
       <c r="E46">
-        <v>-1148.652</v>
+        <v>-1115.91</v>
       </c>
       <c r="F46">
-        <v>1440.648</v>
+        <v>1473.39</v>
       </c>
       <c r="G46">
         <v>306.8</v>
@@ -5047,28 +5047,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M46">
-        <v>78.22718640000001</v>
+        <v>80.005077</v>
       </c>
       <c r="N46">
-        <v>444.6728136000001</v>
+        <v>442.8949230000001</v>
       </c>
       <c r="O46">
-        <v>40.020553224</v>
+        <v>39.86054307000001</v>
       </c>
       <c r="P46">
-        <v>404.6522603760001</v>
+        <v>403.0343799300001</v>
       </c>
       <c r="Q46">
-        <v>947.952260376</v>
+        <v>946.3343799300001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1627506307236071</v>
+        <v>0.1647654176297917</v>
       </c>
       <c r="T46">
-        <v>1.701774177038018</v>
+        <v>1.731091781466185</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.684376929092775</v>
+        <v>6.53583521955738</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1128568296963854</v>
+        <v>0.1128315861875509</v>
       </c>
       <c r="C47">
-        <v>2066.410181305903</v>
+        <v>2034.337793554235</v>
       </c>
       <c r="D47">
-        <v>3233.000181305903</v>
+        <v>3233.669793554235</v>
       </c>
       <c r="E47">
-        <v>-1115.91</v>
+        <v>-1083.168</v>
       </c>
       <c r="F47">
-        <v>1473.39</v>
+        <v>1506.132</v>
       </c>
       <c r="G47">
         <v>306.8</v>
@@ -5129,28 +5129,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M47">
-        <v>80.005077</v>
+        <v>81.78296760000002</v>
       </c>
       <c r="N47">
-        <v>442.8949230000001</v>
+        <v>441.1170324000001</v>
       </c>
       <c r="O47">
-        <v>39.86054307000001</v>
+        <v>39.70053291600001</v>
       </c>
       <c r="P47">
-        <v>403.0343799300001</v>
+        <v>401.4164994840001</v>
       </c>
       <c r="Q47">
-        <v>946.3343799300001</v>
+        <v>944.716499484</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1647654176297917</v>
+        <v>0.1668548262732424</v>
       </c>
       <c r="T47">
-        <v>1.731091781466185</v>
+        <v>1.761495223095394</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.53583521955738</v>
+        <v>6.393751845219175</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1128315861875509</v>
+        <v>0.1128063426787163</v>
       </c>
       <c r="C48">
-        <v>2034.337793554235</v>
+        <v>2002.26568323741</v>
       </c>
       <c r="D48">
-        <v>3233.669793554235</v>
+        <v>3234.33968323741</v>
       </c>
       <c r="E48">
-        <v>-1083.168</v>
+        <v>-1050.426</v>
       </c>
       <c r="F48">
-        <v>1506.132</v>
+        <v>1538.874</v>
       </c>
       <c r="G48">
         <v>306.8</v>
@@ -5211,28 +5211,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M48">
-        <v>81.78296760000002</v>
+        <v>83.56085820000001</v>
       </c>
       <c r="N48">
-        <v>441.1170324000001</v>
+        <v>439.3391418000001</v>
       </c>
       <c r="O48">
-        <v>39.70053291600001</v>
+        <v>39.54052276200001</v>
       </c>
       <c r="P48">
-        <v>401.4164994840001</v>
+        <v>399.7986190380001</v>
       </c>
       <c r="Q48">
-        <v>944.716499484</v>
+        <v>943.098619038</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1668548262732424</v>
+        <v>0.1690230805258799</v>
       </c>
       <c r="T48">
-        <v>1.761495223095394</v>
+        <v>1.793045964408725</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.393751845219175</v>
+        <v>6.257714571916639</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1128063426787163</v>
+        <v>0.1127810991698818</v>
       </c>
       <c r="C49">
-        <v>2002.26568323741</v>
+        <v>1970.193850527886</v>
       </c>
       <c r="D49">
-        <v>3234.33968323741</v>
+        <v>3235.009850527886</v>
       </c>
       <c r="E49">
-        <v>-1050.426</v>
+        <v>-1017.684</v>
       </c>
       <c r="F49">
-        <v>1538.874</v>
+        <v>1571.616</v>
       </c>
       <c r="G49">
         <v>306.8</v>
@@ -5293,28 +5293,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M49">
-        <v>83.56085820000001</v>
+        <v>85.33874880000002</v>
       </c>
       <c r="N49">
-        <v>439.3391418000001</v>
+        <v>437.5612512000001</v>
       </c>
       <c r="O49">
-        <v>39.54052276200001</v>
+        <v>39.380512608</v>
       </c>
       <c r="P49">
-        <v>399.7986190380001</v>
+        <v>398.1807385920001</v>
       </c>
       <c r="Q49">
-        <v>943.098619038</v>
+        <v>941.4807385920001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1690230805258799</v>
+        <v>0.1712747291728496</v>
       </c>
       <c r="T49">
-        <v>1.793045964408725</v>
+        <v>1.825810195772568</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.257714571916639</v>
+        <v>6.127345518335042</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1127810991698818</v>
+        <v>0.1132017556610472</v>
       </c>
       <c r="C50">
-        <v>1970.193850527886</v>
+        <v>1926.320339639141</v>
       </c>
       <c r="D50">
-        <v>3235.009850527886</v>
+        <v>3223.878339639141</v>
       </c>
       <c r="E50">
-        <v>-1017.684</v>
+        <v>-984.942</v>
       </c>
       <c r="F50">
-        <v>1571.616</v>
+        <v>1604.358</v>
       </c>
       <c r="G50">
         <v>306.8</v>
@@ -5375,45 +5375,45 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M50">
-        <v>85.3387488</v>
+        <v>88.72099740000002</v>
       </c>
       <c r="N50">
-        <v>437.5612512000001</v>
+        <v>434.1790026000001</v>
       </c>
       <c r="O50">
-        <v>39.380512608</v>
+        <v>39.07611023400001</v>
       </c>
       <c r="P50">
-        <v>398.1807385920001</v>
+        <v>395.1028923660001</v>
       </c>
       <c r="Q50">
-        <v>941.4807385920001</v>
+        <v>938.4028923660001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1712747291728496</v>
+        <v>0.1736146777667593</v>
       </c>
       <c r="T50">
-        <v>1.825810195772568</v>
+        <v>1.859859298954601</v>
       </c>
       <c r="U50">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V50">
         <v>0.09</v>
       </c>
       <c r="W50">
-        <v>0.04941300000000001</v>
+        <v>0.05032300000000001</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>6.127345518335043</v>
+        <v>5.893757005937357</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1132017556610472</v>
+        <v>0.1131856121522127</v>
       </c>
       <c r="C51">
-        <v>1926.320339639141</v>
+        <v>1894.004119236499</v>
       </c>
       <c r="D51">
-        <v>3223.878339639141</v>
+        <v>3224.304119236499</v>
       </c>
       <c r="E51">
-        <v>-984.942</v>
+        <v>-952.2</v>
       </c>
       <c r="F51">
-        <v>1604.358</v>
+        <v>1637.1</v>
       </c>
       <c r="G51">
         <v>306.8</v>
@@ -5457,28 +5457,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M51">
-        <v>88.72099740000002</v>
+        <v>90.53163000000001</v>
       </c>
       <c r="N51">
-        <v>434.1790026000001</v>
+        <v>432.3683700000001</v>
       </c>
       <c r="O51">
-        <v>39.07611023400001</v>
+        <v>38.9131533</v>
       </c>
       <c r="P51">
-        <v>395.1028923660001</v>
+        <v>393.4552167000001</v>
       </c>
       <c r="Q51">
-        <v>938.4028923660001</v>
+        <v>936.7552167</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1736146777667593</v>
+        <v>0.1760482243044254</v>
       </c>
       <c r="T51">
-        <v>1.859859298954601</v>
+        <v>1.895270366263916</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.893757005937357</v>
+        <v>5.77588186581861</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1131856121522127</v>
+        <v>0.1131694686433782</v>
       </c>
       <c r="C52">
-        <v>1894.004119236499</v>
+        <v>1861.68801131466</v>
       </c>
       <c r="D52">
-        <v>3224.304119236499</v>
+        <v>3224.73001131466</v>
       </c>
       <c r="E52">
-        <v>-952.2</v>
+        <v>-919.4580000000001</v>
       </c>
       <c r="F52">
-        <v>1637.1</v>
+        <v>1669.842</v>
       </c>
       <c r="G52">
         <v>306.8</v>
@@ -5539,28 +5539,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M52">
-        <v>90.53163000000001</v>
+        <v>92.34226260000001</v>
       </c>
       <c r="N52">
-        <v>432.3683700000001</v>
+        <v>430.5577374000001</v>
       </c>
       <c r="O52">
-        <v>38.9131533</v>
+        <v>38.750196366</v>
       </c>
       <c r="P52">
-        <v>393.4552167000001</v>
+        <v>391.8075410340001</v>
       </c>
       <c r="Q52">
-        <v>936.7552167</v>
+        <v>935.107541034</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1760482243044254</v>
+        <v>0.1785810992722003</v>
       </c>
       <c r="T52">
-        <v>1.895270366263916</v>
+        <v>1.932126783259325</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.77588186581861</v>
+        <v>5.662629280214323</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1131694686433782</v>
+        <v>0.1131533251345436</v>
       </c>
       <c r="C53">
-        <v>1861.68801131466</v>
+        <v>1829.372015918203</v>
       </c>
       <c r="D53">
-        <v>3224.73001131466</v>
+        <v>3225.156015918203</v>
       </c>
       <c r="E53">
-        <v>-919.4580000000001</v>
+        <v>-886.7159999999999</v>
       </c>
       <c r="F53">
-        <v>1669.842</v>
+        <v>1702.584</v>
       </c>
       <c r="G53">
         <v>306.8</v>
@@ -5621,28 +5621,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M53">
-        <v>92.34226260000001</v>
+        <v>94.15289520000002</v>
       </c>
       <c r="N53">
-        <v>430.5577374000001</v>
+        <v>428.7471048000001</v>
       </c>
       <c r="O53">
-        <v>38.750196366</v>
+        <v>38.58723943200001</v>
       </c>
       <c r="P53">
-        <v>391.8075410340001</v>
+        <v>390.1598653680001</v>
       </c>
       <c r="Q53">
-        <v>935.107541034</v>
+        <v>933.459865368</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1785810992722003</v>
+        <v>0.1812195106969658</v>
       </c>
       <c r="T53">
-        <v>1.932126783259325</v>
+        <v>1.970518884296209</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.662629280214323</v>
+        <v>5.553732563287125</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1131533251345436</v>
+        <v>0.113137181625709</v>
       </c>
       <c r="C54">
-        <v>1829.372015918203</v>
+        <v>1797.056133091727</v>
       </c>
       <c r="D54">
-        <v>3225.156015918203</v>
+        <v>3225.582133091727</v>
       </c>
       <c r="E54">
-        <v>-886.7159999999999</v>
+        <v>-853.9739999999999</v>
       </c>
       <c r="F54">
-        <v>1702.584</v>
+        <v>1735.326</v>
       </c>
       <c r="G54">
         <v>306.8</v>
@@ -5703,28 +5703,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M54">
-        <v>94.15289520000002</v>
+        <v>95.96352780000002</v>
       </c>
       <c r="N54">
-        <v>428.7471048000001</v>
+        <v>426.9364722000001</v>
       </c>
       <c r="O54">
-        <v>38.58723943200001</v>
+        <v>38.424282498</v>
       </c>
       <c r="P54">
-        <v>390.1598653680001</v>
+        <v>388.5121897020001</v>
       </c>
       <c r="Q54">
-        <v>933.459865368</v>
+        <v>931.8121897020001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1812195106969658</v>
+        <v>0.1839701949483171</v>
       </c>
       <c r="T54">
-        <v>1.970518884296209</v>
+        <v>2.010544691760195</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.553732563287125</v>
+        <v>5.44894515643265</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.113137181625709</v>
+        <v>0.1131210381168745</v>
       </c>
       <c r="C55">
-        <v>1797.056133091727</v>
+        <v>1764.740362879858</v>
       </c>
       <c r="D55">
-        <v>3225.582133091727</v>
+        <v>3226.008362879858</v>
       </c>
       <c r="E55">
-        <v>-853.9739999999999</v>
+        <v>-821.232</v>
       </c>
       <c r="F55">
-        <v>1735.326</v>
+        <v>1768.068</v>
       </c>
       <c r="G55">
         <v>306.8</v>
@@ -5785,28 +5785,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M55">
-        <v>95.96352780000002</v>
+        <v>97.77416040000001</v>
       </c>
       <c r="N55">
-        <v>426.9364722000001</v>
+        <v>425.1258396000001</v>
       </c>
       <c r="O55">
-        <v>38.424282498</v>
+        <v>38.261325564</v>
       </c>
       <c r="P55">
-        <v>388.5121897020001</v>
+        <v>386.8645140360001</v>
       </c>
       <c r="Q55">
-        <v>931.8121897020001</v>
+        <v>930.164514036</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1839701949483171</v>
+        <v>0.1868404741671185</v>
       </c>
       <c r="T55">
-        <v>2.010544691760195</v>
+        <v>2.052310751722615</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.44894515643265</v>
+        <v>5.34803876464686</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1131210381168745</v>
+        <v>0.11310489460804</v>
       </c>
       <c r="C56">
-        <v>1764.740362879858</v>
+        <v>1732.424705327246</v>
       </c>
       <c r="D56">
-        <v>3226.008362879858</v>
+        <v>3226.434705327246</v>
       </c>
       <c r="E56">
-        <v>-821.232</v>
+        <v>-788.4899999999998</v>
       </c>
       <c r="F56">
-        <v>1768.068</v>
+        <v>1800.81</v>
       </c>
       <c r="G56">
         <v>306.8</v>
@@ -5867,28 +5867,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M56">
-        <v>97.77416040000001</v>
+        <v>99.58479300000002</v>
       </c>
       <c r="N56">
-        <v>425.1258396000001</v>
+        <v>423.3152070000001</v>
       </c>
       <c r="O56">
-        <v>38.261325564</v>
+        <v>38.09836863000001</v>
       </c>
       <c r="P56">
-        <v>386.8645140360001</v>
+        <v>385.2168383700001</v>
       </c>
       <c r="Q56">
-        <v>930.164514036</v>
+        <v>928.5168383700001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1868404741671185</v>
+        <v>0.1898383213511999</v>
       </c>
       <c r="T56">
-        <v>2.052310751722615</v>
+        <v>2.095933081016698</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.34803876464686</v>
+        <v>5.250801696198736</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.11310489460804</v>
+        <v>0.1130887510992054</v>
       </c>
       <c r="C57">
-        <v>1732.424705327246</v>
+        <v>1700.109160478562</v>
       </c>
       <c r="D57">
-        <v>3226.434705327246</v>
+        <v>3226.861160478562</v>
       </c>
       <c r="E57">
-        <v>-788.4899999999998</v>
+        <v>-755.7479999999998</v>
       </c>
       <c r="F57">
-        <v>1800.81</v>
+        <v>1833.552</v>
       </c>
       <c r="G57">
         <v>306.8</v>
@@ -5949,28 +5949,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M57">
-        <v>99.58479300000002</v>
+        <v>101.3954256</v>
       </c>
       <c r="N57">
-        <v>423.3152070000001</v>
+        <v>421.5045744000001</v>
       </c>
       <c r="O57">
-        <v>38.09836863000001</v>
+        <v>37.935411696</v>
       </c>
       <c r="P57">
-        <v>385.2168383700001</v>
+        <v>383.5691627040001</v>
       </c>
       <c r="Q57">
-        <v>928.5168383700001</v>
+        <v>926.869162704</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1898383213511999</v>
+        <v>0.192972434316376</v>
       </c>
       <c r="T57">
-        <v>2.095933081016698</v>
+        <v>2.141538243460512</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.250801696198736</v>
+        <v>5.157037380195187</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1130887510992054</v>
+        <v>0.1130726075903709</v>
       </c>
       <c r="C58">
-        <v>1700.109160478562</v>
+        <v>1667.793728378501</v>
       </c>
       <c r="D58">
-        <v>3226.861160478562</v>
+        <v>3227.287728378501</v>
       </c>
       <c r="E58">
-        <v>-755.7479999999998</v>
+        <v>-723.0059999999999</v>
       </c>
       <c r="F58">
-        <v>1833.552</v>
+        <v>1866.294</v>
       </c>
       <c r="G58">
         <v>306.8</v>
@@ -6031,28 +6031,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M58">
-        <v>101.3954256</v>
+        <v>103.2060582</v>
       </c>
       <c r="N58">
-        <v>421.5045744000001</v>
+        <v>419.6939418000001</v>
       </c>
       <c r="O58">
-        <v>37.935411696</v>
+        <v>37.772454762</v>
       </c>
       <c r="P58">
-        <v>383.5691627040001</v>
+        <v>381.9214870380001</v>
       </c>
       <c r="Q58">
-        <v>926.869162704</v>
+        <v>925.2214870380001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.192972434316376</v>
+        <v>0.1962523199776067</v>
       </c>
       <c r="T58">
-        <v>2.141538243460512</v>
+        <v>2.18926457625055</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.157037380195187</v>
+        <v>5.066563040191762</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1130726075903709</v>
+        <v>0.1130564640815363</v>
       </c>
       <c r="C59">
-        <v>1667.793728378501</v>
+        <v>1635.478409071786</v>
       </c>
       <c r="D59">
-        <v>3227.287728378501</v>
+        <v>3227.714409071787</v>
       </c>
       <c r="E59">
-        <v>-723.0059999999999</v>
+        <v>-690.2639999999999</v>
       </c>
       <c r="F59">
-        <v>1866.294</v>
+        <v>1899.036</v>
       </c>
       <c r="G59">
         <v>306.8</v>
@@ -6113,28 +6113,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M59">
-        <v>103.2060582</v>
+        <v>105.0166908</v>
       </c>
       <c r="N59">
-        <v>419.6939418000001</v>
+        <v>417.8833092000001</v>
       </c>
       <c r="O59">
-        <v>37.772454762</v>
+        <v>37.60949782800001</v>
       </c>
       <c r="P59">
-        <v>381.9214870380001</v>
+        <v>380.2738113720001</v>
       </c>
       <c r="Q59">
-        <v>925.2214870380001</v>
+        <v>923.573811372</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1962523199776067</v>
+        <v>0.1996883906703246</v>
       </c>
       <c r="T59">
-        <v>2.18926457625055</v>
+        <v>2.2392635915544</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.066563040191762</v>
+        <v>4.979208505016043</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1130564640815363</v>
+        <v>0.1130403205727018</v>
       </c>
       <c r="C60">
-        <v>1635.478409071785</v>
+        <v>1603.163202603157</v>
       </c>
       <c r="D60">
-        <v>3227.714409071785</v>
+        <v>3228.141202603157</v>
       </c>
       <c r="E60">
-        <v>-690.2640000000001</v>
+        <v>-657.5220000000002</v>
       </c>
       <c r="F60">
-        <v>1899.036</v>
+        <v>1931.778</v>
       </c>
       <c r="G60">
         <v>306.8</v>
@@ -6195,28 +6195,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M60">
-        <v>105.0166908</v>
+        <v>106.8273234</v>
       </c>
       <c r="N60">
-        <v>417.8833092000001</v>
+        <v>416.0726766000001</v>
       </c>
       <c r="O60">
-        <v>37.60949782800001</v>
+        <v>37.44654089400001</v>
       </c>
       <c r="P60">
-        <v>380.2738113720001</v>
+        <v>378.6261357060001</v>
       </c>
       <c r="Q60">
-        <v>923.573811372</v>
+        <v>921.926135706</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1996883906703246</v>
+        <v>0.2032920745675653</v>
       </c>
       <c r="T60">
-        <v>2.2392635915544</v>
+        <v>2.291701583214534</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.979208505016043</v>
+        <v>4.894815140524246</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1130403205727018</v>
+        <v>0.1130241770638672</v>
       </c>
       <c r="C61">
-        <v>1603.163202603157</v>
+        <v>1570.848109017382</v>
       </c>
       <c r="D61">
-        <v>3228.141202603157</v>
+        <v>3228.568109017382</v>
       </c>
       <c r="E61">
-        <v>-657.5220000000002</v>
+        <v>-624.7800000000002</v>
       </c>
       <c r="F61">
-        <v>1931.778</v>
+        <v>1964.52</v>
       </c>
       <c r="G61">
         <v>306.8</v>
@@ -6277,28 +6277,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M61">
-        <v>106.8273234</v>
+        <v>108.637956</v>
       </c>
       <c r="N61">
-        <v>416.0726766000001</v>
+        <v>414.2620440000001</v>
       </c>
       <c r="O61">
-        <v>37.44654089400001</v>
+        <v>37.28358396</v>
       </c>
       <c r="P61">
-        <v>378.6261357060001</v>
+        <v>376.9784600400001</v>
       </c>
       <c r="Q61">
-        <v>921.926135706</v>
+        <v>920.27846004</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2032920745675653</v>
+        <v>0.2070759426596681</v>
       </c>
       <c r="T61">
-        <v>2.291701583214534</v>
+        <v>2.346761474457676</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.894815140524246</v>
+        <v>4.813234888182174</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1130241770638672</v>
+        <v>0.1130080335550327</v>
       </c>
       <c r="C62">
-        <v>1570.848109017382</v>
+        <v>1538.533128359252</v>
       </c>
       <c r="D62">
-        <v>3228.568109017382</v>
+        <v>3228.995128359252</v>
       </c>
       <c r="E62">
-        <v>-624.7800000000002</v>
+        <v>-592.038</v>
       </c>
       <c r="F62">
-        <v>1964.52</v>
+        <v>1997.262</v>
       </c>
       <c r="G62">
         <v>306.8</v>
@@ -6359,28 +6359,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M62">
-        <v>108.637956</v>
+        <v>110.4485886</v>
       </c>
       <c r="N62">
-        <v>414.2620440000001</v>
+        <v>412.4514114000001</v>
       </c>
       <c r="O62">
-        <v>37.28358396</v>
+        <v>37.12062702600001</v>
       </c>
       <c r="P62">
-        <v>376.9784600400001</v>
+        <v>375.3307843740001</v>
       </c>
       <c r="Q62">
-        <v>920.27846004</v>
+        <v>918.6307843740001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2070759426596681</v>
+        <v>0.2110538552693146</v>
       </c>
       <c r="T62">
-        <v>2.346761474457676</v>
+        <v>2.404644949867132</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.813234888182174</v>
+        <v>4.734329398211976</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1130080335550327</v>
+        <v>0.1129918900461982</v>
       </c>
       <c r="C63">
-        <v>1538.533128359252</v>
+        <v>1506.218260673581</v>
       </c>
       <c r="D63">
-        <v>3228.995128359252</v>
+        <v>3229.422260673581</v>
       </c>
       <c r="E63">
-        <v>-592.038</v>
+        <v>-559.296</v>
       </c>
       <c r="F63">
-        <v>1997.262</v>
+        <v>2030.004</v>
       </c>
       <c r="G63">
         <v>306.8</v>
@@ -6441,28 +6441,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M63">
-        <v>110.4485886</v>
+        <v>112.2592212</v>
       </c>
       <c r="N63">
-        <v>412.4514114000001</v>
+        <v>410.6407788000001</v>
       </c>
       <c r="O63">
-        <v>37.12062702600001</v>
+        <v>36.95767009200001</v>
       </c>
       <c r="P63">
-        <v>375.3307843740001</v>
+        <v>373.6831087080001</v>
       </c>
       <c r="Q63">
-        <v>918.6307843740001</v>
+        <v>916.983108708</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2110538552693146</v>
+        <v>0.2152411317005214</v>
       </c>
       <c r="T63">
-        <v>2.404644949867132</v>
+        <v>2.465574923982349</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.734329398211976</v>
+        <v>4.657969246627911</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1129918900461982</v>
+        <v>0.1129757465373636</v>
       </c>
       <c r="C64">
-        <v>1506.218260673581</v>
+        <v>1473.903506005206</v>
       </c>
       <c r="D64">
-        <v>3229.422260673581</v>
+        <v>3229.849506005206</v>
       </c>
       <c r="E64">
-        <v>-559.296</v>
+        <v>-526.5540000000001</v>
       </c>
       <c r="F64">
-        <v>2030.004</v>
+        <v>2062.746</v>
       </c>
       <c r="G64">
         <v>306.8</v>
@@ -6523,28 +6523,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M64">
-        <v>112.2592212</v>
+        <v>114.0698538</v>
       </c>
       <c r="N64">
-        <v>410.6407788000001</v>
+        <v>408.8301462000001</v>
       </c>
       <c r="O64">
-        <v>36.95767009200001</v>
+        <v>36.794713158</v>
       </c>
       <c r="P64">
-        <v>373.6831087080001</v>
+        <v>372.0354330420001</v>
       </c>
       <c r="Q64">
-        <v>916.983108708</v>
+        <v>915.335433042</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2152411317005214</v>
+        <v>0.21965474739828</v>
       </c>
       <c r="T64">
-        <v>2.465574923982349</v>
+        <v>2.529798410211903</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.657969246627911</v>
+        <v>4.584033226840166</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1129757465373636</v>
+        <v>0.1129596030285291</v>
       </c>
       <c r="C65">
-        <v>1473.903506005206</v>
+        <v>1441.58886439899</v>
       </c>
       <c r="D65">
-        <v>3229.849506005206</v>
+        <v>3230.27686439899</v>
       </c>
       <c r="E65">
-        <v>-526.5540000000001</v>
+        <v>-493.8119999999999</v>
       </c>
       <c r="F65">
-        <v>2062.746</v>
+        <v>2095.488</v>
       </c>
       <c r="G65">
         <v>306.8</v>
@@ -6605,28 +6605,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M65">
-        <v>114.0698538</v>
+        <v>115.8804864</v>
       </c>
       <c r="N65">
-        <v>408.8301462000001</v>
+        <v>407.0195136000001</v>
       </c>
       <c r="O65">
-        <v>36.794713158</v>
+        <v>36.63175622400001</v>
       </c>
       <c r="P65">
-        <v>372.0354330420001</v>
+        <v>370.3877573760001</v>
       </c>
       <c r="Q65">
-        <v>915.335433042</v>
+        <v>913.687757376</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.21965474739828</v>
+        <v>0.2243135639681363</v>
       </c>
       <c r="T65">
-        <v>2.529798410211903</v>
+        <v>2.597589867898654</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.584033226840166</v>
+        <v>4.512407707670789</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1129596030285291</v>
+        <v>0.1144222095196945</v>
       </c>
       <c r="C66">
-        <v>1441.58886439899</v>
+        <v>1370.581664889829</v>
       </c>
       <c r="D66">
-        <v>3230.27686439899</v>
+        <v>3192.01166488983</v>
       </c>
       <c r="E66">
-        <v>-493.8119999999999</v>
+        <v>-461.0699999999997</v>
       </c>
       <c r="F66">
-        <v>2095.488</v>
+        <v>2128.23</v>
       </c>
       <c r="G66">
         <v>306.8</v>
@@ -6687,45 +6687,45 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M66">
-        <v>115.8804864</v>
+        <v>123.011694</v>
       </c>
       <c r="N66">
-        <v>407.0195136000001</v>
+        <v>399.8883060000001</v>
       </c>
       <c r="O66">
-        <v>36.63175622400001</v>
+        <v>35.98994754</v>
       </c>
       <c r="P66">
-        <v>370.3877573760001</v>
+        <v>363.8983584600001</v>
       </c>
       <c r="Q66">
-        <v>913.687757376</v>
+        <v>907.19835846</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2243135639681363</v>
+        <v>0.2292385986276986</v>
       </c>
       <c r="T66">
-        <v>2.597589867898654</v>
+        <v>2.669255123167505</v>
       </c>
       <c r="U66">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V66">
         <v>0.09</v>
       </c>
       <c r="W66">
-        <v>0.05032300000000001</v>
+        <v>0.05259800000000001</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>4.512407707670789</v>
+        <v>4.250815373699349</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1144222095196945</v>
+        <v>0.1144288160108599</v>
       </c>
       <c r="C67">
-        <v>1370.581664889829</v>
+        <v>1337.668880241471</v>
       </c>
       <c r="D67">
-        <v>3192.01166488983</v>
+        <v>3191.840880241471</v>
       </c>
       <c r="E67">
-        <v>-461.0699999999997</v>
+        <v>-428.328</v>
       </c>
       <c r="F67">
-        <v>2128.23</v>
+        <v>2160.972</v>
       </c>
       <c r="G67">
         <v>306.8</v>
@@ -6769,28 +6769,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M67">
-        <v>123.011694</v>
+        <v>124.9041816</v>
       </c>
       <c r="N67">
-        <v>399.8883060000001</v>
+        <v>397.9958184000001</v>
       </c>
       <c r="O67">
-        <v>35.98994754</v>
+        <v>35.819623656</v>
       </c>
       <c r="P67">
-        <v>363.8983584600001</v>
+        <v>362.1761947440001</v>
       </c>
       <c r="Q67">
-        <v>907.19835846</v>
+        <v>905.4761947440001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2292385986276986</v>
+        <v>0.2344533412084116</v>
       </c>
       <c r="T67">
-        <v>2.669255123167505</v>
+        <v>2.745135981687464</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.250815373699349</v>
+        <v>4.18640908015845</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1144288160108599</v>
+        <v>0.1144354225020254</v>
       </c>
       <c r="C68">
-        <v>1337.668880241471</v>
+        <v>1304.756113867379</v>
       </c>
       <c r="D68">
-        <v>3191.840880241471</v>
+        <v>3191.670113867379</v>
       </c>
       <c r="E68">
-        <v>-428.328</v>
+        <v>-395.5859999999998</v>
       </c>
       <c r="F68">
-        <v>2160.972</v>
+        <v>2193.714</v>
       </c>
       <c r="G68">
         <v>306.8</v>
@@ -6851,28 +6851,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M68">
-        <v>124.9041816</v>
+        <v>126.7966692</v>
       </c>
       <c r="N68">
-        <v>397.9958184000001</v>
+        <v>396.1033308000001</v>
       </c>
       <c r="O68">
-        <v>35.819623656</v>
+        <v>35.64929977200001</v>
       </c>
       <c r="P68">
-        <v>362.1761947440001</v>
+        <v>360.4540310280001</v>
       </c>
       <c r="Q68">
-        <v>905.4761947440001</v>
+        <v>903.7540310280001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2344533412084116</v>
+        <v>0.2399841287940164</v>
       </c>
       <c r="T68">
-        <v>2.745135981687464</v>
+        <v>2.825615680117725</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.18640908015845</v>
+        <v>4.123925362544145</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1144354225020254</v>
+        <v>0.1144420289931909</v>
       </c>
       <c r="C69">
-        <v>1304.756113867379</v>
+        <v>1271.843365764621</v>
       </c>
       <c r="D69">
-        <v>3191.670113867379</v>
+        <v>3191.499365764621</v>
       </c>
       <c r="E69">
-        <v>-395.5859999999998</v>
+        <v>-362.8440000000001</v>
       </c>
       <c r="F69">
-        <v>2193.714</v>
+        <v>2226.456</v>
       </c>
       <c r="G69">
         <v>306.8</v>
@@ -6933,28 +6933,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M69">
-        <v>126.7966692</v>
+        <v>128.6891568</v>
       </c>
       <c r="N69">
-        <v>396.1033308000001</v>
+        <v>394.2108432000001</v>
       </c>
       <c r="O69">
-        <v>35.64929977200001</v>
+        <v>35.47897588800001</v>
       </c>
       <c r="P69">
-        <v>360.4540310280001</v>
+        <v>358.7318673120001</v>
       </c>
       <c r="Q69">
-        <v>903.7540310280001</v>
+        <v>902.031867312</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2399841287940164</v>
+        <v>0.2458605906037215</v>
       </c>
       <c r="T69">
-        <v>2.825615680117725</v>
+        <v>2.911125359699877</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.123925362544145</v>
+        <v>4.063279401330261</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1144420289931909</v>
+        <v>0.1144486354843563</v>
       </c>
       <c r="C70">
-        <v>1271.843365764621</v>
+        <v>1238.930635930263</v>
       </c>
       <c r="D70">
-        <v>3191.499365764621</v>
+        <v>3191.328635930263</v>
       </c>
       <c r="E70">
-        <v>-362.8440000000001</v>
+        <v>-330.1019999999999</v>
       </c>
       <c r="F70">
-        <v>2226.456</v>
+        <v>2259.198</v>
       </c>
       <c r="G70">
         <v>306.8</v>
@@ -7015,28 +7015,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M70">
-        <v>128.6891568</v>
+        <v>130.5816444</v>
       </c>
       <c r="N70">
-        <v>394.2108432000001</v>
+        <v>392.3183556000001</v>
       </c>
       <c r="O70">
-        <v>35.47897588800001</v>
+        <v>35.308652004</v>
       </c>
       <c r="P70">
-        <v>358.7318673120001</v>
+        <v>357.0097035960001</v>
       </c>
       <c r="Q70">
-        <v>902.031867312</v>
+        <v>900.309703596</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2458605906037215</v>
+        <v>0.2521161789817946</v>
       </c>
       <c r="T70">
-        <v>2.911125359699877</v>
+        <v>3.002151792803457</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.063279401330261</v>
+        <v>4.004391294064605</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1144486354843563</v>
+        <v>0.1166847419755218</v>
       </c>
       <c r="C71">
-        <v>1238.930635930263</v>
+        <v>1149.432271611215</v>
       </c>
       <c r="D71">
-        <v>3191.328635930263</v>
+        <v>3134.572271611215</v>
       </c>
       <c r="E71">
-        <v>-330.1019999999999</v>
+        <v>-297.3599999999997</v>
       </c>
       <c r="F71">
-        <v>2259.198</v>
+        <v>2291.940000000001</v>
       </c>
       <c r="G71">
         <v>306.8</v>
@@ -7097,45 +7097,45 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M71">
-        <v>130.5816444</v>
+        <v>140.495922</v>
       </c>
       <c r="N71">
-        <v>392.3183556000001</v>
+        <v>382.404078</v>
       </c>
       <c r="O71">
-        <v>35.308652004</v>
+        <v>34.41636702</v>
       </c>
       <c r="P71">
-        <v>357.0097035960001</v>
+        <v>347.98771098</v>
       </c>
       <c r="Q71">
-        <v>900.309703596</v>
+        <v>891.2877109799999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2521161789817946</v>
+        <v>0.2587888065850726</v>
       </c>
       <c r="T71">
-        <v>3.002151792803457</v>
+        <v>3.09924665478061</v>
       </c>
       <c r="U71">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V71">
         <v>0.09</v>
       </c>
       <c r="W71">
-        <v>0.05259800000000001</v>
+        <v>0.055783</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>4.004391294064605</v>
+        <v>3.721816210437766</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1166847419755218</v>
+        <v>0.1167231984666872</v>
       </c>
       <c r="C72">
-        <v>1149.432271611215</v>
+        <v>1115.731829940543</v>
       </c>
       <c r="D72">
-        <v>3134.572271611215</v>
+        <v>3133.613829940543</v>
       </c>
       <c r="E72">
-        <v>-297.3599999999997</v>
+        <v>-264.6179999999999</v>
       </c>
       <c r="F72">
-        <v>2291.940000000001</v>
+        <v>2324.682</v>
       </c>
       <c r="G72">
         <v>306.8</v>
@@ -7179,28 +7179,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M72">
-        <v>140.495922</v>
+        <v>142.5030066</v>
       </c>
       <c r="N72">
-        <v>382.404078</v>
+        <v>380.3969934</v>
       </c>
       <c r="O72">
-        <v>34.41636702</v>
+        <v>34.235729406</v>
       </c>
       <c r="P72">
-        <v>347.98771098</v>
+        <v>346.161263994</v>
       </c>
       <c r="Q72">
-        <v>891.2877109799999</v>
+        <v>889.461263994</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2587888065850726</v>
+        <v>0.2659216154023698</v>
       </c>
       <c r="T72">
-        <v>3.09924665478061</v>
+        <v>3.203037714135498</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.721816210437766</v>
+        <v>3.669396263811882</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1167231984666872</v>
+        <v>0.1167616549578527</v>
       </c>
       <c r="C73">
-        <v>1115.731829940543</v>
+        <v>1082.031974206046</v>
       </c>
       <c r="D73">
-        <v>3133.613829940543</v>
+        <v>3132.655974206046</v>
       </c>
       <c r="E73">
-        <v>-264.6179999999999</v>
+        <v>-231.8760000000002</v>
       </c>
       <c r="F73">
-        <v>2324.682</v>
+        <v>2357.424</v>
       </c>
       <c r="G73">
         <v>306.8</v>
@@ -7261,28 +7261,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M73">
-        <v>142.5030066</v>
+        <v>144.5100912</v>
       </c>
       <c r="N73">
-        <v>380.3969934</v>
+        <v>378.3899088000001</v>
       </c>
       <c r="O73">
-        <v>34.235729406</v>
+        <v>34.05509179200001</v>
       </c>
       <c r="P73">
-        <v>346.161263994</v>
+        <v>344.3348170080001</v>
       </c>
       <c r="Q73">
-        <v>889.461263994</v>
+        <v>887.634817008</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2659216154023697</v>
+        <v>0.2735639105637595</v>
       </c>
       <c r="T73">
-        <v>3.203037714135496</v>
+        <v>3.314242420587161</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.669396263811882</v>
+        <v>3.618432426814495</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1167616549578527</v>
+        <v>0.1168001114490181</v>
       </c>
       <c r="C74">
-        <v>1082.031974206046</v>
+        <v>1048.332703870578</v>
       </c>
       <c r="D74">
-        <v>3132.655974206046</v>
+        <v>3131.698703870578</v>
       </c>
       <c r="E74">
-        <v>-231.8760000000002</v>
+        <v>-199.134</v>
       </c>
       <c r="F74">
-        <v>2357.424</v>
+        <v>2390.166</v>
       </c>
       <c r="G74">
         <v>306.8</v>
@@ -7343,28 +7343,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M74">
-        <v>144.5100912</v>
+        <v>146.5171758</v>
       </c>
       <c r="N74">
-        <v>378.3899088000001</v>
+        <v>376.3828242000001</v>
       </c>
       <c r="O74">
-        <v>34.05509179200001</v>
+        <v>33.87445417800001</v>
       </c>
       <c r="P74">
-        <v>344.3348170080001</v>
+        <v>342.5083700220001</v>
       </c>
       <c r="Q74">
-        <v>887.634817008</v>
+        <v>885.808370022</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2735639105637595</v>
+        <v>0.2817723016630301</v>
       </c>
       <c r="T74">
-        <v>3.314242420587161</v>
+        <v>3.433684512701912</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.618432426814495</v>
+        <v>3.568864859323886</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1168001114490181</v>
+        <v>0.1168385679401836</v>
       </c>
       <c r="C75">
-        <v>1048.332703870578</v>
+        <v>1014.634018397645</v>
       </c>
       <c r="D75">
-        <v>3131.698703870578</v>
+        <v>3130.742018397645</v>
       </c>
       <c r="E75">
-        <v>-199.134</v>
+        <v>-166.3919999999998</v>
       </c>
       <c r="F75">
-        <v>2390.166</v>
+        <v>2422.908</v>
       </c>
       <c r="G75">
         <v>306.8</v>
@@ -7425,28 +7425,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M75">
-        <v>146.5171758</v>
+        <v>148.5242604</v>
       </c>
       <c r="N75">
-        <v>376.3828242000001</v>
+        <v>374.3757396000001</v>
       </c>
       <c r="O75">
-        <v>33.87445417800001</v>
+        <v>33.69381656400001</v>
       </c>
       <c r="P75">
-        <v>342.5083700220001</v>
+        <v>340.6819230360001</v>
       </c>
       <c r="Q75">
-        <v>885.808370022</v>
+        <v>883.981923036</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2817723016630301</v>
+        <v>0.2906121074622445</v>
       </c>
       <c r="T75">
-        <v>3.433684512701912</v>
+        <v>3.56231445805626</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.568864859323886</v>
+        <v>3.520636955819509</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1168385679401836</v>
+        <v>0.118788024431349</v>
       </c>
       <c r="C76">
-        <v>1014.634018397645</v>
+        <v>934.1493670793752</v>
       </c>
       <c r="D76">
-        <v>3130.742018397645</v>
+        <v>3082.999367079375</v>
       </c>
       <c r="E76">
-        <v>-166.3919999999998</v>
+        <v>-133.6500000000001</v>
       </c>
       <c r="F76">
-        <v>2422.908</v>
+        <v>2455.65</v>
       </c>
       <c r="G76">
         <v>306.8</v>
@@ -7507,45 +7507,45 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M76">
-        <v>148.5242604</v>
+        <v>157.407165</v>
       </c>
       <c r="N76">
-        <v>374.3757396000001</v>
+        <v>365.4928350000001</v>
       </c>
       <c r="O76">
-        <v>33.69381656400001</v>
+        <v>32.89435515</v>
       </c>
       <c r="P76">
-        <v>340.6819230360001</v>
+        <v>332.59847985</v>
       </c>
       <c r="Q76">
-        <v>883.981923036</v>
+        <v>875.8984798500001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2906121074622445</v>
+        <v>0.3001590977253962</v>
       </c>
       <c r="T76">
-        <v>3.56231445805626</v>
+        <v>3.701234799038956</v>
       </c>
       <c r="U76">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V76">
         <v>0.09</v>
       </c>
       <c r="W76">
-        <v>0.055783</v>
+        <v>0.05833100000000001</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y76">
-        <v>3.520636955819509</v>
+        <v>3.321958056991878</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.118788024431349</v>
+        <v>0.1188519609225145</v>
       </c>
       <c r="C77">
-        <v>934.1493670793752</v>
+        <v>899.8661962395608</v>
       </c>
       <c r="D77">
-        <v>3082.999367079375</v>
+        <v>3081.458196239561</v>
       </c>
       <c r="E77">
-        <v>-133.6500000000001</v>
+        <v>-100.9079999999999</v>
       </c>
       <c r="F77">
-        <v>2455.65</v>
+        <v>2488.392</v>
       </c>
       <c r="G77">
         <v>306.8</v>
@@ -7589,28 +7589,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M77">
-        <v>157.407165</v>
+        <v>159.5059272</v>
       </c>
       <c r="N77">
-        <v>365.4928350000001</v>
+        <v>363.3940728000001</v>
       </c>
       <c r="O77">
-        <v>32.89435515</v>
+        <v>32.705466552</v>
       </c>
       <c r="P77">
-        <v>332.59847985</v>
+        <v>330.688606248</v>
       </c>
       <c r="Q77">
-        <v>875.8984798500001</v>
+        <v>873.988606248</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3001590977253962</v>
+        <v>0.3105016705104771</v>
       </c>
       <c r="T77">
-        <v>3.701234799038956</v>
+        <v>3.851731835103543</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.321958056991878</v>
+        <v>3.278248082557774</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1188519609225145</v>
+        <v>0.11891589741368</v>
       </c>
       <c r="C78">
-        <v>899.8661962395608</v>
+        <v>865.5845654719406</v>
       </c>
       <c r="D78">
-        <v>3081.458196239561</v>
+        <v>3079.918565471941</v>
       </c>
       <c r="E78">
-        <v>-100.9079999999999</v>
+        <v>-68.16599999999971</v>
       </c>
       <c r="F78">
-        <v>2488.392</v>
+        <v>2521.134</v>
       </c>
       <c r="G78">
         <v>306.8</v>
@@ -7671,28 +7671,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M78">
-        <v>159.5059272</v>
+        <v>161.6046894</v>
       </c>
       <c r="N78">
-        <v>363.3940728000001</v>
+        <v>361.2953106000001</v>
       </c>
       <c r="O78">
-        <v>32.705466552</v>
+        <v>32.51657795400001</v>
       </c>
       <c r="P78">
-        <v>330.688606248</v>
+        <v>328.778732646</v>
       </c>
       <c r="Q78">
-        <v>873.988606248</v>
+        <v>872.0787326459999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3105016705104771</v>
+        <v>0.3217435974507824</v>
       </c>
       <c r="T78">
-        <v>3.851731835103543</v>
+        <v>4.015315569956354</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.278248082557774</v>
+        <v>3.235673432134946</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.11891589741368</v>
+        <v>0.1189798339048454</v>
       </c>
       <c r="C79">
-        <v>865.5845654719406</v>
+        <v>831.3044724692072</v>
       </c>
       <c r="D79">
-        <v>3079.918565471941</v>
+        <v>3078.380472469207</v>
       </c>
       <c r="E79">
-        <v>-68.16599999999971</v>
+        <v>-35.42399999999998</v>
       </c>
       <c r="F79">
-        <v>2521.134</v>
+        <v>2553.876</v>
       </c>
       <c r="G79">
         <v>306.8</v>
@@ -7753,28 +7753,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M79">
-        <v>161.6046894</v>
+        <v>163.7034516</v>
       </c>
       <c r="N79">
-        <v>361.2953106000001</v>
+        <v>359.1965484000001</v>
       </c>
       <c r="O79">
-        <v>32.51657795400001</v>
+        <v>32.32768935600001</v>
       </c>
       <c r="P79">
-        <v>328.778732646</v>
+        <v>326.8688590440001</v>
       </c>
       <c r="Q79">
-        <v>872.0787326459999</v>
+        <v>870.1688590440001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3217435974507824</v>
+        <v>0.3340075177492973</v>
       </c>
       <c r="T79">
-        <v>4.015315569956354</v>
+        <v>4.193770553432149</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.235673432134946</v>
+        <v>3.194190439415268</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1189798339048454</v>
+        <v>0.1190437703960109</v>
       </c>
       <c r="C80">
-        <v>831.3044724692072</v>
+        <v>797.0259149286567</v>
       </c>
       <c r="D80">
-        <v>3078.380472469207</v>
+        <v>3076.843914928657</v>
       </c>
       <c r="E80">
-        <v>-35.42399999999998</v>
+        <v>-2.681999999999789</v>
       </c>
       <c r="F80">
-        <v>2553.876</v>
+        <v>2586.618</v>
       </c>
       <c r="G80">
         <v>306.8</v>
@@ -7835,28 +7835,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M80">
-        <v>163.7034516</v>
+        <v>165.8022138</v>
       </c>
       <c r="N80">
-        <v>359.1965484000001</v>
+        <v>357.0977862000001</v>
       </c>
       <c r="O80">
-        <v>32.32768935600001</v>
+        <v>32.13880075800001</v>
       </c>
       <c r="P80">
-        <v>326.8688590440001</v>
+        <v>324.9589854420001</v>
       </c>
       <c r="Q80">
-        <v>870.1688590440001</v>
+        <v>868.258985442</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3340075177492973</v>
+        <v>0.3474394304571946</v>
       </c>
       <c r="T80">
-        <v>4.193770553432149</v>
+        <v>4.389221249619924</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.194190439415268</v>
+        <v>3.153757649042923</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1190437703960109</v>
+        <v>0.1191077068871763</v>
       </c>
       <c r="C81">
-        <v>797.0259149286567</v>
+        <v>762.7488905521832</v>
       </c>
       <c r="D81">
-        <v>3076.843914928657</v>
+        <v>3075.308890552184</v>
       </c>
       <c r="E81">
-        <v>-2.681999999999789</v>
+        <v>30.0600000000004</v>
       </c>
       <c r="F81">
-        <v>2586.618</v>
+        <v>2619.360000000001</v>
       </c>
       <c r="G81">
         <v>306.8</v>
@@ -7917,28 +7917,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M81">
-        <v>165.8022138</v>
+        <v>167.900976</v>
       </c>
       <c r="N81">
-        <v>357.0977862000001</v>
+        <v>354.9990240000001</v>
       </c>
       <c r="O81">
-        <v>32.13880075800001</v>
+        <v>31.94991216000001</v>
       </c>
       <c r="P81">
-        <v>324.9589854420001</v>
+        <v>323.0491118400001</v>
       </c>
       <c r="Q81">
-        <v>868.258985442</v>
+        <v>866.34911184</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3474394304571946</v>
+        <v>0.3622145344358816</v>
       </c>
       <c r="T81">
-        <v>4.389221249619924</v>
+        <v>4.604217015426476</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.153757649042923</v>
+        <v>3.114335678429886</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1191077068871763</v>
+        <v>0.1191716433783418</v>
       </c>
       <c r="C82">
-        <v>762.7488905521832</v>
+        <v>728.4733970462644</v>
       </c>
       <c r="D82">
-        <v>3075.308890552184</v>
+        <v>3073.775397046265</v>
       </c>
       <c r="E82">
-        <v>30.0600000000004</v>
+        <v>62.80200000000013</v>
       </c>
       <c r="F82">
-        <v>2619.360000000001</v>
+        <v>2652.102</v>
       </c>
       <c r="G82">
         <v>306.8</v>
@@ -7999,28 +7999,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M82">
-        <v>167.900976</v>
+        <v>169.9997382</v>
       </c>
       <c r="N82">
-        <v>354.9990240000001</v>
+        <v>352.9002618000001</v>
       </c>
       <c r="O82">
-        <v>31.94991216000001</v>
+        <v>31.76102356200001</v>
       </c>
       <c r="P82">
-        <v>323.0491118400001</v>
+        <v>321.1392382380001</v>
       </c>
       <c r="Q82">
-        <v>866.34911184</v>
+        <v>864.439238238</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3622145344358816</v>
+        <v>0.3785449125175883</v>
       </c>
       <c r="T82">
-        <v>4.604217015426476</v>
+        <v>4.841843914475825</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.114335678429886</v>
+        <v>3.075887089807295</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1191716433783418</v>
+        <v>0.1192355798695072</v>
       </c>
       <c r="C83">
-        <v>728.4733970462644</v>
+        <v>694.1994321219481</v>
       </c>
       <c r="D83">
-        <v>3073.775397046265</v>
+        <v>3072.243432121948</v>
       </c>
       <c r="E83">
-        <v>62.80200000000013</v>
+        <v>95.54400000000032</v>
       </c>
       <c r="F83">
-        <v>2652.102</v>
+        <v>2684.844000000001</v>
       </c>
       <c r="G83">
         <v>306.8</v>
@@ -8081,28 +8081,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M83">
-        <v>169.9997382</v>
+        <v>172.0985004</v>
       </c>
       <c r="N83">
-        <v>352.9002618000001</v>
+        <v>350.8014996000001</v>
       </c>
       <c r="O83">
-        <v>31.76102356200001</v>
+        <v>31.572134964</v>
       </c>
       <c r="P83">
-        <v>321.1392382380001</v>
+        <v>319.2293646360001</v>
       </c>
       <c r="Q83">
-        <v>864.439238238</v>
+        <v>862.5293646360001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3785449125175883</v>
+        <v>0.396689777052818</v>
       </c>
       <c r="T83">
-        <v>4.841843914475825</v>
+        <v>5.105873802308433</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.075887089807295</v>
+        <v>3.038376271638913</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1192355798695072</v>
+        <v>0.1192995163606727</v>
       </c>
       <c r="C84">
-        <v>694.1994321219481</v>
+        <v>659.9269934948475</v>
       </c>
       <c r="D84">
-        <v>3072.243432121948</v>
+        <v>3070.712993494848</v>
       </c>
       <c r="E84">
-        <v>95.54400000000032</v>
+        <v>128.2860000000001</v>
       </c>
       <c r="F84">
-        <v>2684.844000000001</v>
+        <v>2717.586</v>
       </c>
       <c r="G84">
         <v>306.8</v>
@@ -8163,28 +8163,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M84">
-        <v>172.0985004</v>
+        <v>174.1972626</v>
       </c>
       <c r="N84">
-        <v>350.8014996000001</v>
+        <v>348.7027374</v>
       </c>
       <c r="O84">
-        <v>31.572134964</v>
+        <v>31.383246366</v>
       </c>
       <c r="P84">
-        <v>319.2293646360001</v>
+        <v>317.3194910340001</v>
       </c>
       <c r="Q84">
-        <v>862.5293646360001</v>
+        <v>860.619491034</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.396689777052818</v>
+        <v>0.4169693315333688</v>
       </c>
       <c r="T84">
-        <v>5.105873802308433</v>
+        <v>5.400966029886055</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.038376271638913</v>
+        <v>3.001769328607119</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1192995163606727</v>
+        <v>0.1253257728518381</v>
       </c>
       <c r="C85">
-        <v>659.9269934948475</v>
+        <v>489.4731351759442</v>
       </c>
       <c r="D85">
-        <v>3070.712993494848</v>
+        <v>2933.001135175944</v>
       </c>
       <c r="E85">
-        <v>128.2860000000001</v>
+        <v>161.0280000000002</v>
       </c>
       <c r="F85">
-        <v>2717.586</v>
+        <v>2750.328</v>
       </c>
       <c r="G85">
         <v>306.8</v>
@@ -8245,45 +8245,45 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M85">
-        <v>174.1972626</v>
+        <v>197.7485832</v>
       </c>
       <c r="N85">
-        <v>348.7027374</v>
+        <v>325.1514168</v>
       </c>
       <c r="O85">
-        <v>31.383246366</v>
+        <v>29.263627512</v>
       </c>
       <c r="P85">
-        <v>317.3194910340001</v>
+        <v>295.887789288</v>
       </c>
       <c r="Q85">
-        <v>860.619491034</v>
+        <v>839.187789288</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4169693315333688</v>
+        <v>0.4397838303239885</v>
       </c>
       <c r="T85">
-        <v>5.400966029886055</v>
+        <v>5.732944785910879</v>
       </c>
       <c r="U85">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V85">
         <v>0.09</v>
       </c>
       <c r="W85">
-        <v>0.05833100000000001</v>
+        <v>0.065429</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y85">
-        <v>3.001769328607119</v>
+        <v>2.644266732728733</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1253257728518381</v>
+        <v>0.1254606893430036</v>
       </c>
       <c r="C86">
-        <v>489.4731351759447</v>
+        <v>453.7892484960812</v>
       </c>
       <c r="D86">
-        <v>2933.001135175944</v>
+        <v>2930.059248496081</v>
       </c>
       <c r="E86">
-        <v>161.0279999999998</v>
+        <v>193.77</v>
       </c>
       <c r="F86">
-        <v>2750.328</v>
+        <v>2783.07</v>
       </c>
       <c r="G86">
         <v>306.8</v>
@@ -8327,28 +8327,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M86">
-        <v>197.7485832</v>
+        <v>200.102733</v>
       </c>
       <c r="N86">
-        <v>325.1514168000001</v>
+        <v>322.797267</v>
       </c>
       <c r="O86">
-        <v>29.26362751200001</v>
+        <v>29.05175403</v>
       </c>
       <c r="P86">
-        <v>295.8877892880001</v>
+        <v>293.74551297</v>
       </c>
       <c r="Q86">
-        <v>839.187789288</v>
+        <v>837.04551297</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4397838303239882</v>
+        <v>0.4656402622866905</v>
       </c>
       <c r="T86">
-        <v>5.732944785910875</v>
+        <v>6.109187376072343</v>
       </c>
       <c r="U86">
         <v>0.07190000000000001</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.644266732728733</v>
+        <v>2.613157712343689</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1254606893430036</v>
+        <v>0.1255956058341691</v>
       </c>
       <c r="C87">
-        <v>453.7892484960812</v>
+        <v>418.1112575009583</v>
       </c>
       <c r="D87">
-        <v>2930.059248496081</v>
+        <v>2927.123257500959</v>
       </c>
       <c r="E87">
-        <v>193.77</v>
+        <v>226.5120000000002</v>
       </c>
       <c r="F87">
-        <v>2783.07</v>
+        <v>2815.812</v>
       </c>
       <c r="G87">
         <v>306.8</v>
@@ -8409,28 +8409,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M87">
-        <v>200.102733</v>
+        <v>202.4568828</v>
       </c>
       <c r="N87">
-        <v>322.797267</v>
+        <v>320.4431172000001</v>
       </c>
       <c r="O87">
-        <v>29.05175403</v>
+        <v>28.83988054800001</v>
       </c>
       <c r="P87">
-        <v>293.74551297</v>
+        <v>291.6032366520001</v>
       </c>
       <c r="Q87">
-        <v>837.04551297</v>
+        <v>834.903236652</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4656402622866905</v>
+        <v>0.4951904702440645</v>
       </c>
       <c r="T87">
-        <v>6.109187376072343</v>
+        <v>6.539178907685447</v>
       </c>
       <c r="U87">
         <v>0.07190000000000001</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.613157712343689</v>
+        <v>2.582772157548995</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1255956058341691</v>
+        <v>0.1257305223253345</v>
       </c>
       <c r="C88">
-        <v>418.1112575009583</v>
+        <v>382.4391444854577</v>
       </c>
       <c r="D88">
-        <v>2927.123257500959</v>
+        <v>2924.193144485458</v>
       </c>
       <c r="E88">
-        <v>226.5120000000002</v>
+        <v>259.2539999999999</v>
       </c>
       <c r="F88">
-        <v>2815.812</v>
+        <v>2848.554</v>
       </c>
       <c r="G88">
         <v>306.8</v>
@@ -8491,28 +8491,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M88">
-        <v>202.4568828</v>
+        <v>204.8110326</v>
       </c>
       <c r="N88">
-        <v>320.4431172000001</v>
+        <v>318.0889674000001</v>
       </c>
       <c r="O88">
-        <v>28.83988054800001</v>
+        <v>28.62800706600001</v>
       </c>
       <c r="P88">
-        <v>291.6032366520001</v>
+        <v>289.460960334</v>
       </c>
       <c r="Q88">
-        <v>834.903236652</v>
+        <v>832.7609603339999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4951904702440645</v>
+        <v>0.5292868640410345</v>
       </c>
       <c r="T88">
-        <v>6.539178907685447</v>
+        <v>7.035322982623645</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.582772157548995</v>
+        <v>2.553085121255328</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1257305223253345</v>
+        <v>0.1258654388164999</v>
       </c>
       <c r="C89">
-        <v>382.4391444854577</v>
+        <v>346.7728918152798</v>
       </c>
       <c r="D89">
-        <v>2924.193144485458</v>
+        <v>2921.26889181528</v>
       </c>
       <c r="E89">
-        <v>259.2539999999999</v>
+        <v>291.9960000000001</v>
       </c>
       <c r="F89">
-        <v>2848.554</v>
+        <v>2881.296</v>
       </c>
       <c r="G89">
         <v>306.8</v>
@@ -8573,28 +8573,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M89">
-        <v>204.8110326</v>
+        <v>207.1651824</v>
       </c>
       <c r="N89">
-        <v>318.0889674000001</v>
+        <v>315.7348176</v>
       </c>
       <c r="O89">
-        <v>28.62800706600001</v>
+        <v>28.416133584</v>
       </c>
       <c r="P89">
-        <v>289.460960334</v>
+        <v>287.318684016</v>
       </c>
       <c r="Q89">
-        <v>832.7609603339999</v>
+        <v>830.618684016</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5292868640410345</v>
+        <v>0.5690659901374995</v>
       </c>
       <c r="T89">
-        <v>7.035322982623645</v>
+        <v>7.61415773671821</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.553085121255328</v>
+        <v>2.524072790331972</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1258654388164999</v>
+        <v>0.1291589653076654</v>
       </c>
       <c r="C90">
-        <v>346.7728918152798</v>
+        <v>244.4160561305553</v>
       </c>
       <c r="D90">
-        <v>2921.26889181528</v>
+        <v>2851.654056130556</v>
       </c>
       <c r="E90">
-        <v>291.9960000000001</v>
+        <v>324.7380000000003</v>
       </c>
       <c r="F90">
-        <v>2881.296</v>
+        <v>2914.038</v>
       </c>
       <c r="G90">
         <v>306.8</v>
@@ -8655,45 +8655,45 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M90">
-        <v>207.1651824</v>
+        <v>220.8840804</v>
       </c>
       <c r="N90">
-        <v>315.7348176</v>
+        <v>302.0159196000001</v>
       </c>
       <c r="O90">
-        <v>28.416133584</v>
+        <v>27.18143276400001</v>
       </c>
       <c r="P90">
-        <v>287.318684016</v>
+        <v>274.8344868360001</v>
       </c>
       <c r="Q90">
-        <v>830.618684016</v>
+        <v>818.134486836</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5690659901374995</v>
+        <v>0.61607768461514</v>
       </c>
       <c r="T90">
-        <v>7.61415773671821</v>
+        <v>8.298235173375422</v>
       </c>
       <c r="U90">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V90">
         <v>0.09</v>
       </c>
       <c r="W90">
-        <v>0.065429</v>
+        <v>0.06897800000000001</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y90">
-        <v>2.524072790331972</v>
+        <v>2.367305054547517</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1291589653076654</v>
+        <v>0.1293293717988309</v>
       </c>
       <c r="C91">
-        <v>244.4160561305553</v>
+        <v>208.16235995652</v>
       </c>
       <c r="D91">
-        <v>2851.654056130556</v>
+        <v>2848.14235995652</v>
       </c>
       <c r="E91">
-        <v>324.7380000000003</v>
+        <v>357.48</v>
       </c>
       <c r="F91">
-        <v>2914.038</v>
+        <v>2946.78</v>
       </c>
       <c r="G91">
         <v>306.8</v>
@@ -8737,28 +8737,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M91">
-        <v>220.8840804</v>
+        <v>223.365924</v>
       </c>
       <c r="N91">
-        <v>302.0159196000001</v>
+        <v>299.534076</v>
       </c>
       <c r="O91">
-        <v>27.18143276400001</v>
+        <v>26.95806684</v>
       </c>
       <c r="P91">
-        <v>274.8344868360001</v>
+        <v>272.57600916</v>
       </c>
       <c r="Q91">
-        <v>818.134486836</v>
+        <v>815.87600916</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.61607768461514</v>
+        <v>0.6724917179883085</v>
       </c>
       <c r="T91">
-        <v>8.298235173375422</v>
+        <v>9.119128097364078</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.367305054547517</v>
+        <v>2.341001665052544</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1293293717988309</v>
+        <v>0.1294997782899963</v>
       </c>
       <c r="C92">
-        <v>208.16235995652</v>
+        <v>171.917302167145</v>
       </c>
       <c r="D92">
-        <v>2848.14235995652</v>
+        <v>2844.639302167145</v>
       </c>
       <c r="E92">
-        <v>357.48</v>
+        <v>390.2220000000002</v>
       </c>
       <c r="F92">
-        <v>2946.78</v>
+        <v>2979.522</v>
       </c>
       <c r="G92">
         <v>306.8</v>
@@ -8819,28 +8819,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M92">
-        <v>223.365924</v>
+        <v>225.8477676000001</v>
       </c>
       <c r="N92">
-        <v>299.534076</v>
+        <v>297.0522324</v>
       </c>
       <c r="O92">
-        <v>26.95806684</v>
+        <v>26.734700916</v>
       </c>
       <c r="P92">
-        <v>272.57600916</v>
+        <v>270.317531484</v>
       </c>
       <c r="Q92">
-        <v>815.87600916</v>
+        <v>813.617531484</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6724917179883085</v>
+        <v>0.7414422032221814</v>
       </c>
       <c r="T92">
-        <v>9.119128097364078</v>
+        <v>10.12244167112799</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.341001665052544</v>
+        <v>2.315276372029988</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1294997782899963</v>
+        <v>0.1296701847811618</v>
       </c>
       <c r="C93">
-        <v>171.917302167145</v>
+        <v>135.6808509273778</v>
       </c>
       <c r="D93">
-        <v>2844.639302167145</v>
+        <v>2841.144850927378</v>
       </c>
       <c r="E93">
-        <v>390.2220000000002</v>
+        <v>422.9640000000004</v>
       </c>
       <c r="F93">
-        <v>2979.522</v>
+        <v>3012.264000000001</v>
       </c>
       <c r="G93">
         <v>306.8</v>
@@ -8901,28 +8901,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M93">
-        <v>225.8477676000001</v>
+        <v>228.3296112000001</v>
       </c>
       <c r="N93">
-        <v>297.0522324</v>
+        <v>294.5703888</v>
       </c>
       <c r="O93">
-        <v>26.734700916</v>
+        <v>26.511334992</v>
       </c>
       <c r="P93">
-        <v>270.317531484</v>
+        <v>268.059053808</v>
       </c>
       <c r="Q93">
-        <v>813.617531484</v>
+        <v>811.359053808</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7414422032221814</v>
+        <v>0.8276303097645223</v>
       </c>
       <c r="T93">
-        <v>10.12244167112799</v>
+        <v>11.37658363833288</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.315276372029988</v>
+        <v>2.290110324507923</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1296701847811618</v>
+        <v>0.1298405912723272</v>
       </c>
       <c r="C94">
-        <v>135.6808509273778</v>
+        <v>99.45297455840318</v>
       </c>
       <c r="D94">
-        <v>2841.144850927378</v>
+        <v>2837.658974558403</v>
       </c>
       <c r="E94">
-        <v>422.9640000000004</v>
+        <v>455.7060000000001</v>
       </c>
       <c r="F94">
-        <v>3012.264000000001</v>
+        <v>3045.006</v>
       </c>
       <c r="G94">
         <v>306.8</v>
@@ -8983,28 +8983,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M94">
-        <v>228.3296112000001</v>
+        <v>230.8114548</v>
       </c>
       <c r="N94">
-        <v>294.5703888</v>
+        <v>292.0885452000001</v>
       </c>
       <c r="O94">
-        <v>26.511334992</v>
+        <v>26.287969068</v>
       </c>
       <c r="P94">
-        <v>268.059053808</v>
+        <v>265.8005761320001</v>
       </c>
       <c r="Q94">
-        <v>811.359053808</v>
+        <v>809.100576132</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8276303097645223</v>
+        <v>0.938443589604675</v>
       </c>
       <c r="T94">
-        <v>11.37658363833288</v>
+        <v>12.98905188188203</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.290110324507923</v>
+        <v>2.265485482308914</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1298405912723272</v>
+        <v>0.1300109977634927</v>
       </c>
       <c r="C95">
-        <v>99.45297455840318</v>
+        <v>63.23364153668399</v>
       </c>
       <c r="D95">
-        <v>2837.658974558403</v>
+        <v>2834.181641536684</v>
       </c>
       <c r="E95">
-        <v>455.7060000000001</v>
+        <v>488.4480000000003</v>
       </c>
       <c r="F95">
-        <v>3045.006</v>
+        <v>3077.748000000001</v>
       </c>
       <c r="G95">
         <v>306.8</v>
@@ -9065,28 +9065,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M95">
-        <v>230.8114548</v>
+        <v>233.2932984000001</v>
       </c>
       <c r="N95">
-        <v>292.0885452000001</v>
+        <v>289.6067016000001</v>
       </c>
       <c r="O95">
-        <v>26.287969068</v>
+        <v>26.06460314400001</v>
       </c>
       <c r="P95">
-        <v>265.8005761320001</v>
+        <v>263.5420984560001</v>
       </c>
       <c r="Q95">
-        <v>809.100576132</v>
+        <v>806.842098456</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.938443589604675</v>
+        <v>1.086194629391545</v>
       </c>
       <c r="T95">
-        <v>12.98905188188203</v>
+        <v>15.13900953994756</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.265485482308914</v>
+        <v>2.241384572922648</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1300109977634927</v>
+        <v>0.1301814042546581</v>
       </c>
       <c r="C96">
-        <v>63.23364153668399</v>
+        <v>27.02282049301584</v>
       </c>
       <c r="D96">
-        <v>2834.181641536684</v>
+        <v>2830.712820493016</v>
       </c>
       <c r="E96">
-        <v>488.4480000000003</v>
+        <v>521.1900000000005</v>
       </c>
       <c r="F96">
-        <v>3077.748000000001</v>
+        <v>3110.490000000001</v>
       </c>
       <c r="G96">
         <v>306.8</v>
@@ -9147,28 +9147,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M96">
-        <v>233.2932984000001</v>
+        <v>235.7751420000001</v>
       </c>
       <c r="N96">
-        <v>289.6067016000001</v>
+        <v>287.124858</v>
       </c>
       <c r="O96">
-        <v>26.06460314400001</v>
+        <v>25.84123722</v>
       </c>
       <c r="P96">
-        <v>263.5420984560001</v>
+        <v>261.28362078</v>
       </c>
       <c r="Q96">
-        <v>806.842098456</v>
+        <v>804.58362078</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.086194629391545</v>
+        <v>1.293046085093164</v>
       </c>
       <c r="T96">
-        <v>15.13900953994756</v>
+        <v>18.1489502612393</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.241384572922648</v>
+        <v>2.217791051102409</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1301814042546581</v>
+        <v>0.1303518107458236</v>
       </c>
       <c r="C97">
-        <v>27.02282049301584</v>
+        <v>-9.179519788422112</v>
       </c>
       <c r="D97">
-        <v>2830.712820493016</v>
+        <v>2827.252480211578</v>
       </c>
       <c r="E97">
-        <v>521.1900000000005</v>
+        <v>553.9320000000002</v>
       </c>
       <c r="F97">
-        <v>3110.490000000001</v>
+        <v>3143.232</v>
       </c>
       <c r="G97">
         <v>306.8</v>
@@ -9229,28 +9229,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M97">
-        <v>235.7751420000001</v>
+        <v>238.2569856000001</v>
       </c>
       <c r="N97">
-        <v>287.124858</v>
+        <v>284.6430144</v>
       </c>
       <c r="O97">
-        <v>25.84123722</v>
+        <v>25.617871296</v>
       </c>
       <c r="P97">
-        <v>261.28362078</v>
+        <v>259.0251431040001</v>
       </c>
       <c r="Q97">
-        <v>804.58362078</v>
+        <v>802.3251431040001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.293046085093164</v>
+        <v>1.603323268645592</v>
       </c>
       <c r="T97">
-        <v>18.1489502612393</v>
+        <v>22.66386134317692</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.217791051102409</v>
+        <v>2.19468906098676</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1303518107458236</v>
+        <v>0.130522217236989</v>
       </c>
       <c r="C98">
-        <v>-9.179519788421658</v>
+        <v>-45.37341037099895</v>
       </c>
       <c r="D98">
-        <v>2827.252480211578</v>
+        <v>2823.800589629001</v>
       </c>
       <c r="E98">
-        <v>553.9319999999998</v>
+        <v>586.674</v>
       </c>
       <c r="F98">
-        <v>3143.232</v>
+        <v>3175.974</v>
       </c>
       <c r="G98">
         <v>306.8</v>
@@ -9311,28 +9311,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M98">
-        <v>238.2569856</v>
+        <v>240.7388292</v>
       </c>
       <c r="N98">
-        <v>284.6430144000001</v>
+        <v>282.1611708</v>
       </c>
       <c r="O98">
-        <v>25.61787129600001</v>
+        <v>25.394505372</v>
       </c>
       <c r="P98">
-        <v>259.0251431040001</v>
+        <v>256.766665428</v>
       </c>
       <c r="Q98">
-        <v>802.3251431040001</v>
+        <v>800.066665428</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.603323268645588</v>
+        <v>2.120451907899632</v>
       </c>
       <c r="T98">
-        <v>22.66386134317686</v>
+        <v>30.18871314640619</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.19468906098676</v>
+        <v>2.172063400564216</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.130522217236989</v>
+        <v>0.1306926237281545</v>
       </c>
       <c r="C99">
-        <v>-45.37341037099895</v>
+        <v>-81.55888216656604</v>
       </c>
       <c r="D99">
-        <v>2823.800589629001</v>
+        <v>2820.357117833434</v>
       </c>
       <c r="E99">
-        <v>586.674</v>
+        <v>619.4160000000002</v>
       </c>
       <c r="F99">
-        <v>3175.974</v>
+        <v>3208.716</v>
       </c>
       <c r="G99">
         <v>306.8</v>
@@ -9393,28 +9393,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M99">
-        <v>240.7388292</v>
+        <v>243.2206728</v>
       </c>
       <c r="N99">
-        <v>282.1611708</v>
+        <v>279.6793272</v>
       </c>
       <c r="O99">
-        <v>25.394505372</v>
+        <v>25.171139448</v>
       </c>
       <c r="P99">
-        <v>256.766665428</v>
+        <v>254.5081877520001</v>
       </c>
       <c r="Q99">
-        <v>800.066665428</v>
+        <v>797.808187752</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.120451907899632</v>
+        <v>3.154709186407721</v>
       </c>
       <c r="T99">
-        <v>30.18871314640619</v>
+        <v>45.23841675286484</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.172063400564216</v>
+        <v>2.149899488313561</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1306926237281545</v>
+        <v>0.1308630302193199</v>
       </c>
       <c r="C100">
-        <v>-81.55888216656604</v>
+        <v>-117.7359659363742</v>
       </c>
       <c r="D100">
-        <v>2820.357117833434</v>
+        <v>2816.922034063626</v>
       </c>
       <c r="E100">
-        <v>619.4160000000002</v>
+        <v>652.1579999999999</v>
       </c>
       <c r="F100">
-        <v>3208.716</v>
+        <v>3241.458</v>
       </c>
       <c r="G100">
         <v>306.8</v>
@@ -9475,28 +9475,28 @@
         <v>522.9000000000001</v>
       </c>
       <c r="M100">
-        <v>243.2206728</v>
+        <v>245.7025164</v>
       </c>
       <c r="N100">
-        <v>279.6793272</v>
+        <v>277.1974836000001</v>
       </c>
       <c r="O100">
-        <v>25.171139448</v>
+        <v>24.94777352400001</v>
       </c>
       <c r="P100">
-        <v>254.5081877520001</v>
+        <v>252.249710076</v>
       </c>
       <c r="Q100">
-        <v>797.808187752</v>
+        <v>795.549710076</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.154709186407721</v>
+        <v>6.257481021931989</v>
       </c>
       <c r="T100">
-        <v>45.23841675286484</v>
+        <v>90.38752757224081</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.149899488313561</v>
+        <v>2.128183331865949</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1308630302193199</v>
-      </c>
-      <c r="C101">
-        <v>-117.7359659363742</v>
-      </c>
-      <c r="D101">
-        <v>2816.922034063626</v>
-      </c>
-      <c r="E101">
-        <v>652.1579999999999</v>
-      </c>
-      <c r="F101">
-        <v>3241.458</v>
-      </c>
-      <c r="G101">
-        <v>306.8</v>
-      </c>
-      <c r="H101">
-        <v>684.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1066.2</v>
-      </c>
-      <c r="K101">
-        <v>543.3</v>
-      </c>
-      <c r="L101">
-        <v>522.9000000000001</v>
-      </c>
-      <c r="M101">
-        <v>245.7025164</v>
-      </c>
-      <c r="N101">
-        <v>277.1974836000001</v>
-      </c>
-      <c r="O101">
-        <v>24.94777352400001</v>
-      </c>
-      <c r="P101">
-        <v>252.249710076</v>
-      </c>
-      <c r="Q101">
-        <v>795.549710076</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.257481021931989</v>
-      </c>
-      <c r="T101">
-        <v>90.38752757224081</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.09</v>
-      </c>
-      <c r="W101">
-        <v>0.06897800000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.128183331865949</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
